--- a/research/traditional_assets/database/data/mexico/mexico_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_oil_gas_production_and_exploration.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1118988363246748</v>
+        <v>0.1115946398157007</v>
       </c>
       <c r="C2">
-        <v>6069.473153474992</v>
+        <v>6033.914205709836</v>
       </c>
       <c r="D2">
-        <v>5820.373153474991</v>
+        <v>5847.283205709836</v>
       </c>
       <c r="E2">
-        <v>-1020.5</v>
+        <v>-958.0310000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>62.469</v>
       </c>
       <c r="G2">
         <v>249.1</v>
@@ -1457,28 +1457,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.1421907</v>
       </c>
       <c r="N2">
-        <v>705.8000000000001</v>
+        <v>702.6578093000001</v>
       </c>
       <c r="O2">
-        <v>211.74</v>
+        <v>210.79734279</v>
       </c>
       <c r="P2">
-        <v>494.0600000000001</v>
+        <v>491.86046651</v>
       </c>
       <c r="Q2">
-        <v>871.1600000000001</v>
+        <v>868.9604665100001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1118988363246748</v>
+        <v>0.1123662018340411</v>
       </c>
       <c r="T2">
-        <v>0.9618186075065634</v>
+        <v>0.9686193451353977</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>224.6203580196454</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1115946398157007</v>
+        <v>0.1112904433067267</v>
       </c>
       <c r="C3">
-        <v>6033.914205709836</v>
+        <v>5998.605246905902</v>
       </c>
       <c r="D3">
-        <v>5847.283205709836</v>
+        <v>5874.443246905902</v>
       </c>
       <c r="E3">
-        <v>-958.0310000000001</v>
+        <v>-895.5620000000001</v>
       </c>
       <c r="F3">
-        <v>62.469</v>
+        <v>124.938</v>
       </c>
       <c r="G3">
         <v>249.1</v>
@@ -1539,28 +1539,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M3">
-        <v>3.1421907</v>
+        <v>6.2843814</v>
       </c>
       <c r="N3">
-        <v>702.6578093000001</v>
+        <v>699.5156186</v>
       </c>
       <c r="O3">
-        <v>210.79734279</v>
+        <v>209.85468558</v>
       </c>
       <c r="P3">
-        <v>491.86046651</v>
+        <v>489.66093302</v>
       </c>
       <c r="Q3">
-        <v>868.9604665100001</v>
+        <v>866.76093302</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1123662018340411</v>
+        <v>0.1128431054150273</v>
       </c>
       <c r="T3">
-        <v>0.9686193451353977</v>
+        <v>0.9755588733280858</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>224.6203580196454</v>
+        <v>112.3101790098227</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1112904433067267</v>
+        <v>0.1109862467977527</v>
       </c>
       <c r="C4">
-        <v>5998.605246905902</v>
+        <v>5963.549776839896</v>
       </c>
       <c r="D4">
-        <v>5874.443246905902</v>
+        <v>5901.856776839896</v>
       </c>
       <c r="E4">
-        <v>-895.5620000000001</v>
+        <v>-833.0930000000001</v>
       </c>
       <c r="F4">
-        <v>124.938</v>
+        <v>187.407</v>
       </c>
       <c r="G4">
         <v>249.1</v>
@@ -1621,28 +1621,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M4">
-        <v>6.2843814</v>
+        <v>9.426572099999998</v>
       </c>
       <c r="N4">
-        <v>699.5156186</v>
+        <v>696.3734279</v>
       </c>
       <c r="O4">
-        <v>209.85468558</v>
+        <v>208.91202837</v>
       </c>
       <c r="P4">
-        <v>489.66093302</v>
+        <v>487.46139953</v>
       </c>
       <c r="Q4">
-        <v>866.76093302</v>
+        <v>864.56139953</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1128431054150273</v>
+        <v>0.1133298420595388</v>
       </c>
       <c r="T4">
-        <v>0.9755588733280858</v>
+        <v>0.9826414845762931</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>112.3101790098227</v>
+        <v>74.87345267321513</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1109862467977527</v>
+        <v>0.1106820502887787</v>
       </c>
       <c r="C5">
-        <v>5963.549776839896</v>
+        <v>5928.751360922683</v>
       </c>
       <c r="D5">
-        <v>5901.856776839896</v>
+        <v>5929.527360922683</v>
       </c>
       <c r="E5">
-        <v>-833.0930000000001</v>
+        <v>-770.6240000000001</v>
       </c>
       <c r="F5">
-        <v>187.407</v>
+        <v>249.876</v>
       </c>
       <c r="G5">
         <v>249.1</v>
@@ -1703,28 +1703,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M5">
-        <v>9.426572099999998</v>
+        <v>12.5687628</v>
       </c>
       <c r="N5">
-        <v>696.3734279</v>
+        <v>693.2312372000001</v>
       </c>
       <c r="O5">
-        <v>208.91202837</v>
+        <v>207.96937116</v>
       </c>
       <c r="P5">
-        <v>487.46139953</v>
+        <v>485.2618660400001</v>
       </c>
       <c r="Q5">
-        <v>864.56139953</v>
+        <v>862.3618660400001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1133298420595388</v>
+        <v>0.1138267190508111</v>
       </c>
       <c r="T5">
-        <v>0.9826414845762931</v>
+        <v>0.9898716502255048</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>74.87345267321513</v>
+        <v>56.15508950491134</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1106820502887787</v>
+        <v>0.1103778537798046</v>
       </c>
       <c r="C6">
-        <v>5928.751360922683</v>
+        <v>5894.21363174517</v>
       </c>
       <c r="D6">
-        <v>5929.527360922683</v>
+        <v>5957.458631745169</v>
       </c>
       <c r="E6">
-        <v>-770.6240000000001</v>
+        <v>-708.1550000000001</v>
       </c>
       <c r="F6">
-        <v>249.876</v>
+        <v>312.345</v>
       </c>
       <c r="G6">
         <v>249.1</v>
@@ -1785,28 +1785,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M6">
-        <v>12.5687628</v>
+        <v>15.7109535</v>
       </c>
       <c r="N6">
-        <v>693.2312372000001</v>
+        <v>690.0890465000001</v>
       </c>
       <c r="O6">
-        <v>207.96937116</v>
+        <v>207.02671395</v>
       </c>
       <c r="P6">
-        <v>485.2618660400001</v>
+        <v>483.0623325500001</v>
       </c>
       <c r="Q6">
-        <v>862.3618660400001</v>
+        <v>860.1623325500001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1138267190508111</v>
+        <v>0.1143340566103207</v>
       </c>
       <c r="T6">
-        <v>0.9898716502255048</v>
+        <v>0.9972540298883841</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.15508950491134</v>
+        <v>44.92407160392907</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1103778537798046</v>
+        <v>0.1100736572708306</v>
       </c>
       <c r="C7">
-        <v>5894.21363174517</v>
+        <v>5859.940290668045</v>
       </c>
       <c r="D7">
-        <v>5957.458631745169</v>
+        <v>5985.654290668045</v>
       </c>
       <c r="E7">
-        <v>-708.1550000000001</v>
+        <v>-645.6860000000001</v>
       </c>
       <c r="F7">
-        <v>312.345</v>
+        <v>374.814</v>
       </c>
       <c r="G7">
         <v>249.1</v>
@@ -1867,28 +1867,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M7">
-        <v>15.7109535</v>
+        <v>18.8531442</v>
       </c>
       <c r="N7">
-        <v>690.0890465000001</v>
+        <v>686.9468558000001</v>
       </c>
       <c r="O7">
-        <v>207.02671395</v>
+        <v>206.08405674</v>
       </c>
       <c r="P7">
-        <v>483.0623325500001</v>
+        <v>480.86279906</v>
       </c>
       <c r="Q7">
-        <v>860.1623325500001</v>
+        <v>857.9627990600001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1143340566103207</v>
+        <v>0.11485218858599</v>
       </c>
       <c r="T7">
-        <v>0.9972540298883841</v>
+        <v>1.004793481458984</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.92407160392907</v>
+        <v>37.43672633660756</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1100736572708306</v>
+        <v>0.1097694607618566</v>
       </c>
       <c r="C8">
-        <v>5859.940290668045</v>
+        <v>5825.935109456905</v>
       </c>
       <c r="D8">
-        <v>5985.654290668045</v>
+        <v>6014.118109456905</v>
       </c>
       <c r="E8">
-        <v>-645.6860000000001</v>
+        <v>-583.2170000000002</v>
       </c>
       <c r="F8">
-        <v>374.814</v>
+        <v>437.2829999999999</v>
       </c>
       <c r="G8">
         <v>249.1</v>
@@ -1949,28 +1949,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M8">
-        <v>18.8531442</v>
+        <v>21.99533489999999</v>
       </c>
       <c r="N8">
-        <v>686.9468558000001</v>
+        <v>683.8046651000001</v>
       </c>
       <c r="O8">
-        <v>206.08405674</v>
+        <v>205.14139953</v>
       </c>
       <c r="P8">
-        <v>480.86279906</v>
+        <v>478.66326557</v>
       </c>
       <c r="Q8">
-        <v>857.9627990600001</v>
+        <v>855.76326557</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.11485218858599</v>
+        <v>0.115381463184792</v>
       </c>
       <c r="T8">
-        <v>1.004793481458984</v>
+        <v>1.012495071773038</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.43672633660757</v>
+        <v>32.08862257423506</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1097694607618566</v>
+        <v>0.1094652642528826</v>
       </c>
       <c r="C9">
-        <v>5825.935109456906</v>
+        <v>5792.201931964251</v>
       </c>
       <c r="D9">
-        <v>6014.118109456906</v>
+        <v>6042.853931964251</v>
       </c>
       <c r="E9">
-        <v>-583.2170000000001</v>
+        <v>-520.748</v>
       </c>
       <c r="F9">
-        <v>437.283</v>
+        <v>499.752</v>
       </c>
       <c r="G9">
         <v>249.1</v>
@@ -2031,28 +2031,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M9">
-        <v>21.9953349</v>
+        <v>25.1375256</v>
       </c>
       <c r="N9">
-        <v>683.8046651000001</v>
+        <v>680.6624744000001</v>
       </c>
       <c r="O9">
-        <v>205.14139953</v>
+        <v>204.19874232</v>
       </c>
       <c r="P9">
-        <v>478.66326557</v>
+        <v>476.4637320800001</v>
       </c>
       <c r="Q9">
-        <v>855.76326557</v>
+        <v>853.5637320800001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.115381463184792</v>
+        <v>0.1159222437531332</v>
       </c>
       <c r="T9">
-        <v>1.012495071773038</v>
+        <v>1.020364087963485</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.08862257423505</v>
+        <v>28.07754475245567</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1094652642528826</v>
+        <v>0.1091610677439085</v>
       </c>
       <c r="C10">
-        <v>5792.201931964251</v>
+        <v>5758.744675859938</v>
       </c>
       <c r="D10">
-        <v>6042.853931964251</v>
+        <v>6071.865675859937</v>
       </c>
       <c r="E10">
-        <v>-520.748</v>
+        <v>-458.2790000000002</v>
       </c>
       <c r="F10">
-        <v>499.752</v>
+        <v>562.2209999999999</v>
       </c>
       <c r="G10">
         <v>249.1</v>
@@ -2113,28 +2113,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M10">
-        <v>25.1375256</v>
+        <v>28.27971629999999</v>
       </c>
       <c r="N10">
-        <v>680.6624744000001</v>
+        <v>677.5202837</v>
       </c>
       <c r="O10">
-        <v>204.19874232</v>
+        <v>203.25608511</v>
       </c>
       <c r="P10">
-        <v>476.4637320800001</v>
+        <v>474.26419859</v>
       </c>
       <c r="Q10">
-        <v>853.5637320800001</v>
+        <v>851.3641985900001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1159222437531332</v>
+        <v>0.1164749096086907</v>
       </c>
       <c r="T10">
-        <v>1.020364087963485</v>
+        <v>1.02840604956471</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.07754475245567</v>
+        <v>24.95781755773838</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1091610677439085</v>
+        <v>0.1088568712349345</v>
       </c>
       <c r="C11">
-        <v>5758.744675859938</v>
+        <v>5725.567334411696</v>
       </c>
       <c r="D11">
-        <v>6071.865675859937</v>
+        <v>6101.157334411695</v>
       </c>
       <c r="E11">
-        <v>-458.2790000000002</v>
+        <v>-395.8100000000002</v>
       </c>
       <c r="F11">
-        <v>562.2209999999999</v>
+        <v>624.6899999999999</v>
       </c>
       <c r="G11">
         <v>249.1</v>
@@ -2195,28 +2195,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M11">
-        <v>28.27971629999999</v>
+        <v>31.42190699999999</v>
       </c>
       <c r="N11">
-        <v>677.5202837</v>
+        <v>674.378093</v>
       </c>
       <c r="O11">
-        <v>203.25608511</v>
+        <v>202.3134279</v>
       </c>
       <c r="P11">
-        <v>474.26419859</v>
+        <v>472.0646651000001</v>
       </c>
       <c r="Q11">
-        <v>851.3641985900001</v>
+        <v>849.1646651000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1164749096086907</v>
+        <v>0.117039856927705</v>
       </c>
       <c r="T11">
-        <v>1.02840604956471</v>
+        <v>1.036626721423741</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.95781755773838</v>
+        <v>22.46203580196454</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1088568712349345</v>
+        <v>0.1085526747259605</v>
       </c>
       <c r="C12">
-        <v>5725.567334411695</v>
+        <v>5692.673978317461</v>
       </c>
       <c r="D12">
-        <v>6101.157334411695</v>
+        <v>6130.73297831746</v>
       </c>
       <c r="E12">
-        <v>-395.8100000000001</v>
+        <v>-333.3410000000001</v>
       </c>
       <c r="F12">
-        <v>624.6900000000001</v>
+        <v>687.159</v>
       </c>
       <c r="G12">
         <v>249.1</v>
@@ -2277,28 +2277,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M12">
-        <v>31.421907</v>
+        <v>34.5640977</v>
       </c>
       <c r="N12">
-        <v>674.378093</v>
+        <v>671.2359023</v>
       </c>
       <c r="O12">
-        <v>202.3134279</v>
+        <v>201.37077069</v>
       </c>
       <c r="P12">
-        <v>472.0646651000001</v>
+        <v>469.86513161</v>
       </c>
       <c r="Q12">
-        <v>849.1646651000001</v>
+        <v>846.9651316100001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.117039856927705</v>
+        <v>0.1176174996920904</v>
       </c>
       <c r="T12">
-        <v>1.036626721423741</v>
+        <v>1.04503212748185</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.46203580196454</v>
+        <v>20.42003254724049</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1085526747259605</v>
+        <v>0.1082484782169865</v>
       </c>
       <c r="C13">
-        <v>5692.673978317461</v>
+        <v>5660.068757591249</v>
       </c>
       <c r="D13">
-        <v>6130.73297831746</v>
+        <v>6160.596757591248</v>
       </c>
       <c r="E13">
-        <v>-333.3410000000001</v>
+        <v>-270.8720000000002</v>
       </c>
       <c r="F13">
-        <v>687.159</v>
+        <v>749.6279999999999</v>
       </c>
       <c r="G13">
         <v>249.1</v>
@@ -2359,28 +2359,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M13">
-        <v>34.5640977</v>
+        <v>37.70628839999999</v>
       </c>
       <c r="N13">
-        <v>671.2359023</v>
+        <v>668.0937116000001</v>
       </c>
       <c r="O13">
-        <v>201.37077069</v>
+        <v>200.42811348</v>
       </c>
       <c r="P13">
-        <v>469.86513161</v>
+        <v>467.6655981200001</v>
       </c>
       <c r="Q13">
-        <v>846.9651316100001</v>
+        <v>844.76559812</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1176174996920904</v>
+        <v>0.118208270701121</v>
       </c>
       <c r="T13">
-        <v>1.04503212748185</v>
+        <v>1.053628565495826</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.42003254724049</v>
+        <v>18.71836316830379</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1082484782169865</v>
+        <v>0.1079442817080124</v>
       </c>
       <c r="C14">
-        <v>5660.068757591249</v>
+        <v>5627.75590350442</v>
       </c>
       <c r="D14">
-        <v>6160.596757591248</v>
+        <v>6190.752903504419</v>
       </c>
       <c r="E14">
-        <v>-270.8720000000002</v>
+        <v>-208.4030000000001</v>
       </c>
       <c r="F14">
-        <v>749.6279999999999</v>
+        <v>812.097</v>
       </c>
       <c r="G14">
         <v>249.1</v>
@@ -2441,28 +2441,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M14">
-        <v>37.70628839999999</v>
+        <v>40.8484791</v>
       </c>
       <c r="N14">
-        <v>668.0937116000001</v>
+        <v>664.9515209000001</v>
       </c>
       <c r="O14">
-        <v>200.42811348</v>
+        <v>199.48545627</v>
       </c>
       <c r="P14">
-        <v>467.6655981200001</v>
+        <v>465.4660646300001</v>
       </c>
       <c r="Q14">
-        <v>844.76559812</v>
+        <v>842.5660646300001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.118208270701121</v>
+        <v>0.1188126226528879</v>
       </c>
       <c r="T14">
-        <v>1.053628565495826</v>
+        <v>1.062422622774491</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.71836316830379</v>
+        <v>17.27848907843426</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1079442817080124</v>
+        <v>0.1076400851990384</v>
       </c>
       <c r="C15">
-        <v>5627.75590350442</v>
+        <v>5595.739730584226</v>
       </c>
       <c r="D15">
-        <v>6190.752903504419</v>
+        <v>6221.205730584225</v>
       </c>
       <c r="E15">
-        <v>-208.4030000000001</v>
+        <v>-145.9340000000001</v>
       </c>
       <c r="F15">
-        <v>812.097</v>
+        <v>874.566</v>
       </c>
       <c r="G15">
         <v>249.1</v>
@@ -2523,28 +2523,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M15">
-        <v>40.8484791</v>
+        <v>43.9906698</v>
       </c>
       <c r="N15">
-        <v>664.9515209000001</v>
+        <v>661.8093302000001</v>
       </c>
       <c r="O15">
-        <v>199.48545627</v>
+        <v>198.54279906</v>
       </c>
       <c r="P15">
-        <v>465.4660646300001</v>
+        <v>463.2665311400001</v>
       </c>
       <c r="Q15">
-        <v>842.5660646300001</v>
+        <v>840.3665311400001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1188126226528879</v>
+        <v>0.1194310293012075</v>
       </c>
       <c r="T15">
-        <v>1.062422622774491</v>
+        <v>1.071421193013125</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.27848907843426</v>
+        <v>16.04431128711753</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1076400851990384</v>
+        <v>0.1073358886900644</v>
       </c>
       <c r="C16">
-        <v>5595.739730584226</v>
+        <v>5564.024638671663</v>
       </c>
       <c r="D16">
-        <v>6221.205730584225</v>
+        <v>6251.959638671662</v>
       </c>
       <c r="E16">
-        <v>-145.9340000000001</v>
+        <v>-83.46500000000003</v>
       </c>
       <c r="F16">
-        <v>874.566</v>
+        <v>937.0350000000001</v>
       </c>
       <c r="G16">
         <v>249.1</v>
@@ -2605,28 +2605,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M16">
-        <v>43.9906698</v>
+        <v>47.1328605</v>
       </c>
       <c r="N16">
-        <v>661.8093302000001</v>
+        <v>658.6671395000001</v>
       </c>
       <c r="O16">
-        <v>198.54279906</v>
+        <v>197.60014185</v>
       </c>
       <c r="P16">
-        <v>463.2665311400001</v>
+        <v>461.0669976500001</v>
       </c>
       <c r="Q16">
-        <v>840.3665311400001</v>
+        <v>838.1669976500001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1194310293012075</v>
+        <v>0.1200639866941934</v>
       </c>
       <c r="T16">
-        <v>1.071421193013125</v>
+        <v>1.080631494316198</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.04431128711753</v>
+        <v>14.97469053464302</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1073358886900644</v>
+        <v>0.1070316921810904</v>
       </c>
       <c r="C17">
-        <v>5564.024638671663</v>
+        <v>5532.615115040628</v>
       </c>
       <c r="D17">
-        <v>6251.959638671662</v>
+        <v>6283.019115040627</v>
       </c>
       <c r="E17">
-        <v>-83.46500000000026</v>
+        <v>-20.99600000000009</v>
       </c>
       <c r="F17">
-        <v>937.0349999999999</v>
+        <v>999.504</v>
       </c>
       <c r="G17">
         <v>249.1</v>
@@ -2687,28 +2687,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M17">
-        <v>47.13286049999999</v>
+        <v>50.2750512</v>
       </c>
       <c r="N17">
-        <v>658.6671395000001</v>
+        <v>655.5249488000001</v>
       </c>
       <c r="O17">
-        <v>197.60014185</v>
+        <v>196.65748464</v>
       </c>
       <c r="P17">
-        <v>461.0669976500001</v>
+        <v>458.8674641600001</v>
       </c>
       <c r="Q17">
-        <v>838.1669976500001</v>
+        <v>835.9674641600001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1200639866941934</v>
+        <v>0.1207120145012981</v>
       </c>
       <c r="T17">
-        <v>1.080631494316198</v>
+        <v>1.090061088507439</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.97469053464303</v>
+        <v>14.03877237622783</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1070316921810904</v>
+        <v>0.1067274956721163</v>
       </c>
       <c r="C18">
-        <v>5532.615115040628</v>
+        <v>5501.515736580598</v>
       </c>
       <c r="D18">
-        <v>6283.019115040627</v>
+        <v>6314.388736580598</v>
       </c>
       <c r="E18">
-        <v>-20.99600000000009</v>
+        <v>41.47299999999984</v>
       </c>
       <c r="F18">
-        <v>999.504</v>
+        <v>1061.973</v>
       </c>
       <c r="G18">
         <v>249.1</v>
@@ -2769,28 +2769,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M18">
-        <v>50.2750512</v>
+        <v>53.41724189999999</v>
       </c>
       <c r="N18">
-        <v>655.5249488000001</v>
+        <v>652.3827581</v>
       </c>
       <c r="O18">
-        <v>196.65748464</v>
+        <v>195.71482743</v>
       </c>
       <c r="P18">
-        <v>458.8674641600001</v>
+        <v>456.66793067</v>
       </c>
       <c r="Q18">
-        <v>835.9674641600001</v>
+        <v>833.7679306700001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1207120145012981</v>
+        <v>0.1213756574362848</v>
       </c>
       <c r="T18">
-        <v>1.090061088507439</v>
+        <v>1.099717901835818</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.03877237622783</v>
+        <v>13.21296223644973</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1067274956721163</v>
+        <v>0.1064232991631423</v>
       </c>
       <c r="C19">
-        <v>5501.515736580598</v>
+        <v>5470.731172044983</v>
       </c>
       <c r="D19">
-        <v>6314.388736580598</v>
+        <v>6346.073172044983</v>
       </c>
       <c r="E19">
-        <v>41.47299999999984</v>
+        <v>103.9419999999999</v>
       </c>
       <c r="F19">
-        <v>1061.973</v>
+        <v>1124.442</v>
       </c>
       <c r="G19">
         <v>249.1</v>
@@ -2851,28 +2851,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M19">
-        <v>53.41724189999999</v>
+        <v>56.5594326</v>
       </c>
       <c r="N19">
-        <v>652.3827581</v>
+        <v>649.2405674</v>
       </c>
       <c r="O19">
-        <v>195.71482743</v>
+        <v>194.77217022</v>
       </c>
       <c r="P19">
-        <v>456.66793067</v>
+        <v>454.46839718</v>
       </c>
       <c r="Q19">
-        <v>833.7679306700001</v>
+        <v>831.56839718</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1213756574362848</v>
+        <v>0.1220554867843199</v>
       </c>
       <c r="T19">
-        <v>1.099717901835818</v>
+        <v>1.109610247196596</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.21296223644973</v>
+        <v>12.47890877886919</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1064232991631423</v>
+        <v>0.1061191026541683</v>
       </c>
       <c r="C20">
-        <v>5470.731172044982</v>
+        <v>5440.266184367543</v>
       </c>
       <c r="D20">
-        <v>6346.073172044981</v>
+        <v>6378.077184367543</v>
       </c>
       <c r="E20">
-        <v>103.9419999999997</v>
+        <v>166.4109999999999</v>
       </c>
       <c r="F20">
-        <v>1124.442</v>
+        <v>1186.911</v>
       </c>
       <c r="G20">
         <v>249.1</v>
@@ -2933,28 +2933,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M20">
-        <v>56.55943259999999</v>
+        <v>59.7016233</v>
       </c>
       <c r="N20">
-        <v>649.2405674</v>
+        <v>646.0983767</v>
       </c>
       <c r="O20">
-        <v>194.77217022</v>
+        <v>193.82951301</v>
       </c>
       <c r="P20">
-        <v>454.46839718</v>
+        <v>452.26886369</v>
       </c>
       <c r="Q20">
-        <v>831.56839718</v>
+        <v>829.36886369</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1220554867843199</v>
+        <v>0.1227521020421831</v>
       </c>
       <c r="T20">
-        <v>1.109610247196596</v>
+        <v>1.119746847998382</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.47890877886919</v>
+        <v>11.82212410629712</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1061191026541683</v>
+        <v>0.1058149061451943</v>
       </c>
       <c r="C21">
-        <v>5440.266184367543</v>
+        <v>5410.125633049234</v>
       </c>
       <c r="D21">
-        <v>6378.077184367543</v>
+        <v>6410.405633049234</v>
       </c>
       <c r="E21">
-        <v>166.4109999999999</v>
+        <v>228.88</v>
       </c>
       <c r="F21">
-        <v>1186.911</v>
+        <v>1249.38</v>
       </c>
       <c r="G21">
         <v>249.1</v>
@@ -3015,28 +3015,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M21">
-        <v>59.7016233</v>
+        <v>62.843814</v>
       </c>
       <c r="N21">
-        <v>646.0983767</v>
+        <v>642.9561860000001</v>
       </c>
       <c r="O21">
-        <v>193.82951301</v>
+        <v>192.8868558</v>
       </c>
       <c r="P21">
-        <v>452.26886369</v>
+        <v>450.0693302000001</v>
       </c>
       <c r="Q21">
-        <v>829.36886369</v>
+        <v>827.1693302000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1227521020421831</v>
+        <v>0.1234661326814928</v>
       </c>
       <c r="T21">
-        <v>1.119746847998382</v>
+        <v>1.130136863820212</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.82212410629712</v>
+        <v>11.23101790098227</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1058149061451943</v>
+        <v>0.1055107096362203</v>
       </c>
       <c r="C22">
-        <v>5410.125633049234</v>
+        <v>5380.314476618022</v>
       </c>
       <c r="D22">
-        <v>6410.405633049234</v>
+        <v>6443.063476618022</v>
       </c>
       <c r="E22">
-        <v>228.88</v>
+        <v>291.349</v>
       </c>
       <c r="F22">
-        <v>1249.38</v>
+        <v>1311.849</v>
       </c>
       <c r="G22">
         <v>249.1</v>
@@ -3097,28 +3097,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M22">
-        <v>62.843814</v>
+        <v>65.98600470000001</v>
       </c>
       <c r="N22">
-        <v>642.9561860000001</v>
+        <v>639.8139953000001</v>
       </c>
       <c r="O22">
-        <v>192.8868558</v>
+        <v>191.94419859</v>
       </c>
       <c r="P22">
-        <v>450.0693302000001</v>
+        <v>447.8697967100001</v>
       </c>
       <c r="Q22">
-        <v>827.1693302000001</v>
+        <v>824.9697967100001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1234661326814928</v>
+        <v>0.1241982400458484</v>
       </c>
       <c r="T22">
-        <v>1.130136863820212</v>
+        <v>1.140789918017278</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.23101790098227</v>
+        <v>10.69620752474502</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1055107096362202</v>
+        <v>0.1052065131272462</v>
       </c>
       <c r="C23">
-        <v>5380.314476618025</v>
+        <v>5350.837775164262</v>
       </c>
       <c r="D23">
-        <v>6443.063476618025</v>
+        <v>6476.055775164262</v>
       </c>
       <c r="E23">
-        <v>291.3489999999998</v>
+        <v>353.8179999999999</v>
       </c>
       <c r="F23">
-        <v>1311.849</v>
+        <v>1374.318</v>
       </c>
       <c r="G23">
         <v>249.1</v>
@@ -3179,28 +3179,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M23">
-        <v>65.9860047</v>
+        <v>69.1281954</v>
       </c>
       <c r="N23">
-        <v>639.8139953000001</v>
+        <v>636.6718046000001</v>
       </c>
       <c r="O23">
-        <v>191.94419859</v>
+        <v>191.00154138</v>
       </c>
       <c r="P23">
-        <v>447.8697967100001</v>
+        <v>445.67026322</v>
       </c>
       <c r="Q23">
-        <v>824.9697967100001</v>
+        <v>822.7702632200001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1241982400458484</v>
+        <v>0.1249491193939054</v>
       </c>
       <c r="T23">
-        <v>1.140789918017278</v>
+        <v>1.151716127450167</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.69620752474502</v>
+        <v>10.21001627362024</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1052065131272462</v>
+        <v>0.1049023166182722</v>
       </c>
       <c r="C24">
-        <v>5350.837775164262</v>
+        <v>5321.700692954387</v>
       </c>
       <c r="D24">
-        <v>6476.055775164262</v>
+        <v>6509.387692954387</v>
       </c>
       <c r="E24">
-        <v>353.8179999999999</v>
+        <v>416.2869999999999</v>
       </c>
       <c r="F24">
-        <v>1374.318</v>
+        <v>1436.787</v>
       </c>
       <c r="G24">
         <v>249.1</v>
@@ -3261,28 +3261,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M24">
-        <v>69.1281954</v>
+        <v>72.2703861</v>
       </c>
       <c r="N24">
-        <v>636.6718046000001</v>
+        <v>633.5296139000001</v>
       </c>
       <c r="O24">
-        <v>191.00154138</v>
+        <v>190.05888417</v>
       </c>
       <c r="P24">
-        <v>445.67026322</v>
+        <v>443.47072973</v>
       </c>
       <c r="Q24">
-        <v>822.7702632200001</v>
+        <v>820.57072973</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1249491193939054</v>
+        <v>0.1257195021016522</v>
       </c>
       <c r="T24">
-        <v>1.151716127450167</v>
+        <v>1.162926134530663</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.21001627362024</v>
+        <v>9.766102522593277</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1049023166182722</v>
+        <v>0.1045981201092982</v>
       </c>
       <c r="C25">
-        <v>5321.700692954387</v>
+        <v>5292.908501125709</v>
       </c>
       <c r="D25">
-        <v>6509.387692954387</v>
+        <v>6543.064501125709</v>
       </c>
       <c r="E25">
-        <v>416.2869999999999</v>
+        <v>478.756</v>
       </c>
       <c r="F25">
-        <v>1436.787</v>
+        <v>1499.256</v>
       </c>
       <c r="G25">
         <v>249.1</v>
@@ -3343,28 +3343,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M25">
-        <v>72.2703861</v>
+        <v>75.4125768</v>
       </c>
       <c r="N25">
-        <v>633.5296139000001</v>
+        <v>630.3874232000001</v>
       </c>
       <c r="O25">
-        <v>190.05888417</v>
+        <v>189.11622696</v>
       </c>
       <c r="P25">
-        <v>443.47072973</v>
+        <v>441.2711962400001</v>
       </c>
       <c r="Q25">
-        <v>820.57072973</v>
+        <v>818.37119624</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1257195021016522</v>
+        <v>0.1265101580385502</v>
       </c>
       <c r="T25">
-        <v>1.162926134530663</v>
+        <v>1.174431141797488</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.766102522593277</v>
+        <v>9.359181584151891</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1045981201092982</v>
+        <v>0.1042939236003242</v>
       </c>
       <c r="C26">
-        <v>5292.90850112571</v>
+        <v>5264.466580465334</v>
       </c>
       <c r="D26">
-        <v>6543.064501125709</v>
+        <v>6577.091580465334</v>
       </c>
       <c r="E26">
-        <v>478.7559999999997</v>
+        <v>541.2249999999998</v>
       </c>
       <c r="F26">
-        <v>1499.256</v>
+        <v>1561.725</v>
       </c>
       <c r="G26">
         <v>249.1</v>
@@ -3425,28 +3425,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M26">
-        <v>75.41257679999998</v>
+        <v>78.5547675</v>
       </c>
       <c r="N26">
-        <v>630.3874232000001</v>
+        <v>627.2452325</v>
       </c>
       <c r="O26">
-        <v>189.11622696</v>
+        <v>188.17356975</v>
       </c>
       <c r="P26">
-        <v>441.2711962400001</v>
+        <v>439.07166275</v>
       </c>
       <c r="Q26">
-        <v>818.37119624</v>
+        <v>816.17166275</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1265101580385502</v>
+        <v>0.1273218981337655</v>
       </c>
       <c r="T26">
-        <v>1.174431141797488</v>
+        <v>1.186242949258095</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.359181584151893</v>
+        <v>8.984814320785814</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1042939236003242</v>
+        <v>0.1042627270913501</v>
       </c>
       <c r="C27">
-        <v>5264.466580465334</v>
+        <v>5205.507206285432</v>
       </c>
       <c r="D27">
-        <v>6577.091580465334</v>
+        <v>6580.601206285432</v>
       </c>
       <c r="E27">
-        <v>541.2249999999998</v>
+        <v>603.6939999999998</v>
       </c>
       <c r="F27">
-        <v>1561.725</v>
+        <v>1624.194</v>
       </c>
       <c r="G27">
         <v>249.1</v>
@@ -3507,45 +3507,45 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M27">
-        <v>78.5547675</v>
+        <v>84.13324919999999</v>
       </c>
       <c r="N27">
-        <v>627.2452325</v>
+        <v>621.6667508</v>
       </c>
       <c r="O27">
-        <v>188.17356975</v>
+        <v>186.50002524</v>
       </c>
       <c r="P27">
-        <v>439.07166275</v>
+        <v>435.16672556</v>
       </c>
       <c r="Q27">
-        <v>816.17166275</v>
+        <v>812.2667255600001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1273218981337655</v>
+        <v>0.1281555771504732</v>
       </c>
       <c r="T27">
-        <v>1.186242949258095</v>
+        <v>1.198373994758178</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>8.984814320785814</v>
+        <v>8.389073365301575</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1042627270913501</v>
+        <v>0.1039690305823761</v>
       </c>
       <c r="C28">
-        <v>5205.507206285432</v>
+        <v>5176.263783227088</v>
       </c>
       <c r="D28">
-        <v>6580.601206285432</v>
+        <v>6613.826783227088</v>
       </c>
       <c r="E28">
-        <v>603.6939999999998</v>
+        <v>666.1629999999999</v>
       </c>
       <c r="F28">
-        <v>1624.194</v>
+        <v>1686.663</v>
       </c>
       <c r="G28">
         <v>249.1</v>
@@ -3589,28 +3589,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M28">
-        <v>84.13324919999999</v>
+        <v>87.3691434</v>
       </c>
       <c r="N28">
-        <v>621.6667508</v>
+        <v>618.4308566000001</v>
       </c>
       <c r="O28">
-        <v>186.50002524</v>
+        <v>185.52925698</v>
       </c>
       <c r="P28">
-        <v>435.16672556</v>
+        <v>432.9015996200001</v>
       </c>
       <c r="Q28">
-        <v>812.2667255600001</v>
+        <v>810.0015996200001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1281555771504732</v>
+        <v>0.1290120966881864</v>
       </c>
       <c r="T28">
-        <v>1.198373994758178</v>
+        <v>1.210837397669222</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.389073365301575</v>
+        <v>8.078366944364479</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1039690305823761</v>
+        <v>0.1036753340734021</v>
       </c>
       <c r="C29">
-        <v>5176.263783227088</v>
+        <v>5147.357575879467</v>
       </c>
       <c r="D29">
-        <v>6613.826783227088</v>
+        <v>6647.389575879466</v>
       </c>
       <c r="E29">
-        <v>666.1629999999999</v>
+        <v>728.6319999999999</v>
       </c>
       <c r="F29">
-        <v>1686.663</v>
+        <v>1749.132</v>
       </c>
       <c r="G29">
         <v>249.1</v>
@@ -3671,28 +3671,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M29">
-        <v>87.3691434</v>
+        <v>90.6050376</v>
       </c>
       <c r="N29">
-        <v>618.4308566000001</v>
+        <v>615.1949624000001</v>
       </c>
       <c r="O29">
-        <v>185.52925698</v>
+        <v>184.55848872</v>
       </c>
       <c r="P29">
-        <v>432.9015996200001</v>
+        <v>430.6364736800001</v>
       </c>
       <c r="Q29">
-        <v>810.0015996200001</v>
+        <v>807.7364736800001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1290120966881864</v>
+        <v>0.1298924084352807</v>
       </c>
       <c r="T29">
-        <v>1.210837397669222</v>
+        <v>1.223647006216683</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.078366944364479</v>
+        <v>7.789853839208606</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1036753340734021</v>
+        <v>0.103381637564428</v>
       </c>
       <c r="C30">
-        <v>5147.357575879467</v>
+        <v>5118.793744172772</v>
       </c>
       <c r="D30">
-        <v>6647.389575879466</v>
+        <v>6681.294744172772</v>
       </c>
       <c r="E30">
-        <v>728.6319999999999</v>
+        <v>791.101</v>
       </c>
       <c r="F30">
-        <v>1749.132</v>
+        <v>1811.601</v>
       </c>
       <c r="G30">
         <v>249.1</v>
@@ -3753,28 +3753,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M30">
-        <v>90.6050376</v>
+        <v>93.84093180000001</v>
       </c>
       <c r="N30">
-        <v>615.1949624000001</v>
+        <v>611.9590682</v>
       </c>
       <c r="O30">
-        <v>184.55848872</v>
+        <v>183.58772046</v>
       </c>
       <c r="P30">
-        <v>430.6364736800001</v>
+        <v>428.37134774</v>
       </c>
       <c r="Q30">
-        <v>807.7364736800001</v>
+        <v>805.4713477400001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1298924084352807</v>
+        <v>0.1307975176963775</v>
       </c>
       <c r="T30">
-        <v>1.223647006216683</v>
+        <v>1.236817448807736</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.789853839208606</v>
+        <v>7.521238189580722</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.103381637564428</v>
+        <v>0.103087941055454</v>
       </c>
       <c r="C31">
-        <v>5118.793744172773</v>
+        <v>5090.577553850302</v>
       </c>
       <c r="D31">
-        <v>6681.294744172772</v>
+        <v>6715.547553850301</v>
       </c>
       <c r="E31">
-        <v>791.1009999999995</v>
+        <v>853.5699999999996</v>
       </c>
       <c r="F31">
-        <v>1811.601</v>
+        <v>1874.07</v>
       </c>
       <c r="G31">
         <v>249.1</v>
@@ -3835,28 +3835,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M31">
-        <v>93.84093179999998</v>
+        <v>97.07682599999998</v>
       </c>
       <c r="N31">
-        <v>611.9590682</v>
+        <v>608.7231740000001</v>
       </c>
       <c r="O31">
-        <v>183.58772046</v>
+        <v>182.6169522</v>
       </c>
       <c r="P31">
-        <v>428.37134774</v>
+        <v>426.1062218000001</v>
       </c>
       <c r="Q31">
-        <v>805.4713477400001</v>
+        <v>803.2062218000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1307975176963775</v>
+        <v>0.1317284872220772</v>
       </c>
       <c r="T31">
-        <v>1.236817448807736</v>
+        <v>1.250364189758532</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.521238189580724</v>
+        <v>7.270530249928033</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.103087941055454</v>
+        <v>0.10279424454648</v>
       </c>
       <c r="C32">
-        <v>5090.577553850302</v>
+        <v>5062.714379194761</v>
       </c>
       <c r="D32">
-        <v>6715.547553850301</v>
+        <v>6750.15337919476</v>
       </c>
       <c r="E32">
-        <v>853.5699999999996</v>
+        <v>916.0389999999996</v>
       </c>
       <c r="F32">
-        <v>1874.07</v>
+        <v>1936.539</v>
       </c>
       <c r="G32">
         <v>249.1</v>
@@ -3917,28 +3917,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M32">
-        <v>97.07682599999998</v>
+        <v>100.3127202</v>
       </c>
       <c r="N32">
-        <v>608.7231740000001</v>
+        <v>605.4872798000001</v>
       </c>
       <c r="O32">
-        <v>182.6169522</v>
+        <v>181.64618394</v>
       </c>
       <c r="P32">
-        <v>426.1062218000001</v>
+        <v>423.8410958600001</v>
       </c>
       <c r="Q32">
-        <v>803.2062218000001</v>
+        <v>800.9410958600001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1317284872220772</v>
+        <v>0.1326864413717102</v>
       </c>
       <c r="T32">
-        <v>1.250364189758532</v>
+        <v>1.264303589867323</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.270530249928033</v>
+        <v>7.035997016059387</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.10279424454648</v>
+        <v>0.102500548037506</v>
       </c>
       <c r="C33">
-        <v>5062.714379194761</v>
+        <v>5035.209705839321</v>
       </c>
       <c r="D33">
-        <v>6750.15337919476</v>
+        <v>6785.11770583932</v>
       </c>
       <c r="E33">
-        <v>916.0389999999996</v>
+        <v>978.5079999999999</v>
       </c>
       <c r="F33">
-        <v>1936.539</v>
+        <v>1999.008</v>
       </c>
       <c r="G33">
         <v>249.1</v>
@@ -3999,28 +3999,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M33">
-        <v>100.3127202</v>
+        <v>103.5486144</v>
       </c>
       <c r="N33">
-        <v>605.4872798000001</v>
+        <v>602.2513856</v>
       </c>
       <c r="O33">
-        <v>181.64618394</v>
+        <v>180.67541568</v>
       </c>
       <c r="P33">
-        <v>423.8410958600001</v>
+        <v>421.57596992</v>
       </c>
       <c r="Q33">
-        <v>800.9410958600001</v>
+        <v>798.6759699200001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1326864413717102</v>
+        <v>0.1336725706433911</v>
       </c>
       <c r="T33">
-        <v>1.264303589867323</v>
+        <v>1.278652972332255</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.035997016059387</v>
+        <v>6.816122109307529</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.102500548037506</v>
+        <v>0.102599551528532</v>
       </c>
       <c r="C34">
-        <v>5035.209705839321</v>
+        <v>4960.914021969062</v>
       </c>
       <c r="D34">
-        <v>6785.11770583932</v>
+        <v>6773.291021969061</v>
       </c>
       <c r="E34">
-        <v>978.5079999999999</v>
+        <v>1040.977</v>
       </c>
       <c r="F34">
-        <v>1999.008</v>
+        <v>2061.477</v>
       </c>
       <c r="G34">
         <v>249.1</v>
@@ -4081,45 +4081,45 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M34">
-        <v>103.5486144</v>
+        <v>110.2890195</v>
       </c>
       <c r="N34">
-        <v>602.2513856</v>
+        <v>595.5109805000001</v>
       </c>
       <c r="O34">
-        <v>180.67541568</v>
+        <v>178.65329415</v>
       </c>
       <c r="P34">
-        <v>421.57596992</v>
+        <v>416.8576863500001</v>
       </c>
       <c r="Q34">
-        <v>798.6759699200001</v>
+        <v>793.9576863500001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1336725706433911</v>
+        <v>0.1346881366097492</v>
       </c>
       <c r="T34">
-        <v>1.278652972332255</v>
+        <v>1.293430694572259</v>
       </c>
       <c r="U34">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>6.816122109307529</v>
+        <v>6.399549140973187</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.102599551528532</v>
+        <v>0.1023177550195579</v>
       </c>
       <c r="C35">
-        <v>4960.914021969062</v>
+        <v>4932.216529057333</v>
       </c>
       <c r="D35">
-        <v>6773.291021969061</v>
+        <v>6807.062529057333</v>
       </c>
       <c r="E35">
-        <v>1040.977</v>
+        <v>1103.446</v>
       </c>
       <c r="F35">
-        <v>2061.477</v>
+        <v>2123.946</v>
       </c>
       <c r="G35">
         <v>249.1</v>
@@ -4163,28 +4163,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M35">
-        <v>110.2890195</v>
+        <v>113.631111</v>
       </c>
       <c r="N35">
-        <v>595.5109805000001</v>
+        <v>592.168889</v>
       </c>
       <c r="O35">
-        <v>178.65329415</v>
+        <v>177.6506667</v>
       </c>
       <c r="P35">
-        <v>416.8576863500001</v>
+        <v>414.5182223</v>
       </c>
       <c r="Q35">
-        <v>793.9576863500001</v>
+        <v>791.6182223000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1346881366097492</v>
+        <v>0.1357344773023605</v>
       </c>
       <c r="T35">
-        <v>1.293430694572259</v>
+        <v>1.308656226577112</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.399549140973187</v>
+        <v>6.211327107415152</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1023177550195579</v>
+        <v>0.1020359585105839</v>
       </c>
       <c r="C36">
-        <v>4932.216529057333</v>
+        <v>4903.857491932691</v>
       </c>
       <c r="D36">
-        <v>6807.062529057333</v>
+        <v>6841.172491932691</v>
       </c>
       <c r="E36">
-        <v>1103.446</v>
+        <v>1165.915</v>
       </c>
       <c r="F36">
-        <v>2123.946</v>
+        <v>2186.415</v>
       </c>
       <c r="G36">
         <v>249.1</v>
@@ -4245,28 +4245,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M36">
-        <v>113.631111</v>
+        <v>116.9732025</v>
       </c>
       <c r="N36">
-        <v>592.168889</v>
+        <v>588.8267975000001</v>
       </c>
       <c r="O36">
-        <v>177.6506667</v>
+        <v>176.64803925</v>
       </c>
       <c r="P36">
-        <v>414.5182223</v>
+        <v>412.1787582500001</v>
       </c>
       <c r="Q36">
-        <v>791.6182223000001</v>
+        <v>789.2787582500001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1357344773023605</v>
+        <v>0.136813013093206</v>
       </c>
       <c r="T36">
-        <v>1.308656226577112</v>
+        <v>1.324350236489807</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.211327107415152</v>
+        <v>6.033860618631863</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1020359585105839</v>
+        <v>0.1017541620016099</v>
       </c>
       <c r="C37">
-        <v>4903.857491932691</v>
+        <v>4875.842024191115</v>
       </c>
       <c r="D37">
-        <v>6841.172491932691</v>
+        <v>6875.626024191115</v>
       </c>
       <c r="E37">
-        <v>1165.915</v>
+        <v>1228.384</v>
       </c>
       <c r="F37">
-        <v>2186.415</v>
+        <v>2248.884</v>
       </c>
       <c r="G37">
         <v>249.1</v>
@@ -4327,28 +4327,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M37">
-        <v>116.9732025</v>
+        <v>120.315294</v>
       </c>
       <c r="N37">
-        <v>588.8267975000001</v>
+        <v>585.4847060000001</v>
       </c>
       <c r="O37">
-        <v>176.64803925</v>
+        <v>175.6454118</v>
       </c>
       <c r="P37">
-        <v>412.1787582500001</v>
+        <v>409.8392942</v>
       </c>
       <c r="Q37">
-        <v>789.2787582500001</v>
+        <v>786.9392942000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.136813013093206</v>
+        <v>0.1379252531275155</v>
       </c>
       <c r="T37">
-        <v>1.324350236489807</v>
+        <v>1.340534684212273</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.033860618631863</v>
+        <v>5.866253379225422</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1017541620016099</v>
+        <v>0.1014723654926358</v>
       </c>
       <c r="C38">
-        <v>4875.842024191114</v>
+        <v>4848.175342962437</v>
       </c>
       <c r="D38">
-        <v>6875.626024191113</v>
+        <v>6910.428342962436</v>
       </c>
       <c r="E38">
-        <v>1228.384</v>
+        <v>1290.853</v>
       </c>
       <c r="F38">
-        <v>2248.884</v>
+        <v>2311.353</v>
       </c>
       <c r="G38">
         <v>249.1</v>
@@ -4409,28 +4409,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M38">
-        <v>120.315294</v>
+        <v>123.6573855</v>
       </c>
       <c r="N38">
-        <v>585.4847060000001</v>
+        <v>582.1426145</v>
       </c>
       <c r="O38">
-        <v>175.6454118</v>
+        <v>174.64278435</v>
       </c>
       <c r="P38">
-        <v>409.8392942</v>
+        <v>407.49983015</v>
       </c>
       <c r="Q38">
-        <v>786.9392942000001</v>
+        <v>784.5998301500001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1379252531275155</v>
+        <v>0.1390728023692633</v>
       </c>
       <c r="T38">
-        <v>1.340534684212273</v>
+        <v>1.357232923925928</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.866253379225422</v>
+        <v>5.707705990597708</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1014723654926358</v>
+        <v>0.1014033689836618</v>
       </c>
       <c r="C39">
-        <v>4848.175342962437</v>
+        <v>4794.281280774558</v>
       </c>
       <c r="D39">
-        <v>6910.428342962436</v>
+        <v>6919.003280774557</v>
       </c>
       <c r="E39">
-        <v>1290.853</v>
+        <v>1353.322</v>
       </c>
       <c r="F39">
-        <v>2311.353</v>
+        <v>2373.822</v>
       </c>
       <c r="G39">
         <v>249.1</v>
@@ -4491,45 +4491,45 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M39">
-        <v>123.6573855</v>
+        <v>128.8985346</v>
       </c>
       <c r="N39">
-        <v>582.1426145</v>
+        <v>576.9014654</v>
       </c>
       <c r="O39">
-        <v>174.64278435</v>
+        <v>173.07043962</v>
       </c>
       <c r="P39">
-        <v>407.49983015</v>
+        <v>403.83102578</v>
       </c>
       <c r="Q39">
-        <v>784.5998301500001</v>
+        <v>780.93102578</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1390728023692633</v>
+        <v>0.1402573693284868</v>
       </c>
       <c r="T39">
-        <v>1.357232923925928</v>
+        <v>1.374469816533573</v>
       </c>
       <c r="U39">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y39">
-        <v>5.707705990597708</v>
+        <v>5.475624701167083</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1014033689836618</v>
+        <v>0.1011271724746878</v>
       </c>
       <c r="C40">
-        <v>4794.281280774558</v>
+        <v>4766.352353333011</v>
       </c>
       <c r="D40">
-        <v>6919.003280774557</v>
+        <v>6953.543353333011</v>
       </c>
       <c r="E40">
-        <v>1353.322</v>
+        <v>1415.791</v>
       </c>
       <c r="F40">
-        <v>2373.822</v>
+        <v>2436.291</v>
       </c>
       <c r="G40">
         <v>249.1</v>
@@ -4573,28 +4573,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M40">
-        <v>128.8985346</v>
+        <v>132.2906013</v>
       </c>
       <c r="N40">
-        <v>576.9014654</v>
+        <v>573.5093987</v>
       </c>
       <c r="O40">
-        <v>173.07043962</v>
+        <v>172.05281961</v>
       </c>
       <c r="P40">
-        <v>403.83102578</v>
+        <v>401.45657909</v>
       </c>
       <c r="Q40">
-        <v>780.93102578</v>
+        <v>778.55657909</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1402573693284868</v>
+        <v>0.1414807745486686</v>
       </c>
       <c r="T40">
-        <v>1.374469816533573</v>
+        <v>1.39227185316114</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.475624701167083</v>
+        <v>5.335224067803825</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1011271724746878</v>
+        <v>0.1008509759657138</v>
       </c>
       <c r="C41">
-        <v>4766.352353333011</v>
+        <v>4738.770008210597</v>
       </c>
       <c r="D41">
-        <v>6953.543353333011</v>
+        <v>6988.430008210596</v>
       </c>
       <c r="E41">
-        <v>1415.791</v>
+        <v>1478.26</v>
       </c>
       <c r="F41">
-        <v>2436.291</v>
+        <v>2498.76</v>
       </c>
       <c r="G41">
         <v>249.1</v>
@@ -4655,28 +4655,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M41">
-        <v>132.2906013</v>
+        <v>135.682668</v>
       </c>
       <c r="N41">
-        <v>573.5093987</v>
+        <v>570.117332</v>
       </c>
       <c r="O41">
-        <v>172.05281961</v>
+        <v>171.0351996</v>
       </c>
       <c r="P41">
-        <v>401.45657909</v>
+        <v>399.0821324</v>
       </c>
       <c r="Q41">
-        <v>778.55657909</v>
+        <v>776.1821324</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1414807745486686</v>
+        <v>0.1427449599428563</v>
       </c>
       <c r="T41">
-        <v>1.39227185316114</v>
+        <v>1.410667291009627</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.335224067803825</v>
+        <v>5.20184346610873</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1008509759657138</v>
+        <v>0.1005747794567398</v>
       </c>
       <c r="C42">
-        <v>4738.770008210597</v>
+        <v>4711.539488230428</v>
       </c>
       <c r="D42">
-        <v>6988.430008210596</v>
+        <v>7023.668488230428</v>
       </c>
       <c r="E42">
-        <v>1478.26</v>
+        <v>1540.729</v>
       </c>
       <c r="F42">
-        <v>2498.76</v>
+        <v>2561.229</v>
       </c>
       <c r="G42">
         <v>249.1</v>
@@ -4737,28 +4737,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M42">
-        <v>135.682668</v>
+        <v>139.0747347</v>
       </c>
       <c r="N42">
-        <v>570.117332</v>
+        <v>566.7252653</v>
       </c>
       <c r="O42">
-        <v>171.0351996</v>
+        <v>170.01757959</v>
       </c>
       <c r="P42">
-        <v>399.0821324</v>
+        <v>396.7076857100001</v>
       </c>
       <c r="Q42">
-        <v>776.1821324</v>
+        <v>773.8076857100001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1427449599428563</v>
+        <v>0.14405199907922</v>
       </c>
       <c r="T42">
-        <v>1.410667291009627</v>
+        <v>1.429686303022468</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.20184346610873</v>
+        <v>5.074969235228028</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1005747794567398</v>
+        <v>0.1002985829477657</v>
       </c>
       <c r="C43">
-        <v>4711.539488230428</v>
+        <v>4684.666142497248</v>
       </c>
       <c r="D43">
-        <v>7023.668488230428</v>
+        <v>7059.264142497248</v>
       </c>
       <c r="E43">
-        <v>1540.729</v>
+        <v>1603.198</v>
       </c>
       <c r="F43">
-        <v>2561.229</v>
+        <v>2623.698</v>
       </c>
       <c r="G43">
         <v>249.1</v>
@@ -4819,28 +4819,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M43">
-        <v>139.0747347</v>
+        <v>142.4668014</v>
       </c>
       <c r="N43">
-        <v>566.7252653</v>
+        <v>563.3331986000001</v>
       </c>
       <c r="O43">
-        <v>170.01757959</v>
+        <v>168.99995958</v>
       </c>
       <c r="P43">
-        <v>396.7076857100001</v>
+        <v>394.3332390200001</v>
       </c>
       <c r="Q43">
-        <v>773.8076857100001</v>
+        <v>771.4332390200001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.14405199907922</v>
+        <v>0.1454041085306306</v>
       </c>
       <c r="T43">
-        <v>1.429686303022468</v>
+        <v>1.449361143035752</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.074969235228028</v>
+        <v>4.954136634389267</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1002985829477657</v>
+        <v>0.1000223864387917</v>
       </c>
       <c r="C44">
-        <v>4684.666142497248</v>
+        <v>4658.155429104278</v>
       </c>
       <c r="D44">
-        <v>7059.264142497247</v>
+        <v>7095.222429104278</v>
       </c>
       <c r="E44">
-        <v>1603.198</v>
+        <v>1665.667</v>
       </c>
       <c r="F44">
-        <v>2623.698</v>
+        <v>2686.167</v>
       </c>
       <c r="G44">
         <v>249.1</v>
@@ -4901,28 +4901,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M44">
-        <v>142.4668014</v>
+        <v>145.8588681</v>
       </c>
       <c r="N44">
-        <v>563.3331986000001</v>
+        <v>559.9411319000001</v>
       </c>
       <c r="O44">
-        <v>168.99995958</v>
+        <v>167.98233957</v>
       </c>
       <c r="P44">
-        <v>394.3332390200001</v>
+        <v>391.9587923300001</v>
       </c>
       <c r="Q44">
-        <v>771.4332390200001</v>
+        <v>769.0587923300001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1454041085306306</v>
+        <v>0.1468036604189328</v>
       </c>
       <c r="T44">
-        <v>1.449361143035752</v>
+        <v>1.469726328312661</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.954136634389267</v>
+        <v>4.838924154519749</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1000223864387917</v>
+        <v>0.09974618992981768</v>
       </c>
       <c r="C45">
-        <v>4658.155429104278</v>
+        <v>4632.012917923272</v>
       </c>
       <c r="D45">
-        <v>7095.222429104278</v>
+        <v>7131.548917923272</v>
       </c>
       <c r="E45">
-        <v>1665.667</v>
+        <v>1728.136</v>
       </c>
       <c r="F45">
-        <v>2686.167</v>
+        <v>2748.636</v>
       </c>
       <c r="G45">
         <v>249.1</v>
@@ -4983,28 +4983,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M45">
-        <v>145.8588681</v>
+        <v>149.2509348</v>
       </c>
       <c r="N45">
-        <v>559.9411319000001</v>
+        <v>556.5490652000001</v>
       </c>
       <c r="O45">
-        <v>167.98233957</v>
+        <v>166.96471956</v>
       </c>
       <c r="P45">
-        <v>391.9587923300001</v>
+        <v>389.58434564</v>
       </c>
       <c r="Q45">
-        <v>769.0587923300001</v>
+        <v>766.6843456400001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1468036604189328</v>
+        <v>0.1482531963032458</v>
       </c>
       <c r="T45">
-        <v>1.469726328312661</v>
+        <v>1.490818841635173</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.838924154519749</v>
+        <v>4.728948605553391</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09974618992981768</v>
+        <v>0.09946999342084367</v>
       </c>
       <c r="C46">
-        <v>4632.012917923272</v>
+        <v>4606.244293480664</v>
       </c>
       <c r="D46">
-        <v>7131.548917923272</v>
+        <v>7168.249293480664</v>
       </c>
       <c r="E46">
-        <v>1728.136</v>
+        <v>1790.605</v>
       </c>
       <c r="F46">
-        <v>2748.636</v>
+        <v>2811.105</v>
       </c>
       <c r="G46">
         <v>249.1</v>
@@ -5065,28 +5065,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M46">
-        <v>149.2509348</v>
+        <v>152.6430015</v>
       </c>
       <c r="N46">
-        <v>556.5490652000001</v>
+        <v>553.1569985000001</v>
       </c>
       <c r="O46">
-        <v>166.96471956</v>
+        <v>165.94709955</v>
       </c>
       <c r="P46">
-        <v>389.58434564</v>
+        <v>387.2098989500001</v>
       </c>
       <c r="Q46">
-        <v>766.6843456400001</v>
+        <v>764.3098989500002</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1482531963032458</v>
+        <v>0.1497554425833521</v>
       </c>
       <c r="T46">
-        <v>1.490818841635173</v>
+        <v>1.512678355442141</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.728948605553391</v>
+        <v>4.623860858763315</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09946999342084367</v>
+        <v>0.09919379691186964</v>
       </c>
       <c r="C47">
-        <v>4606.244293480664</v>
+        <v>4580.855357923036</v>
       </c>
       <c r="D47">
-        <v>7168.249293480664</v>
+        <v>7205.329357923035</v>
       </c>
       <c r="E47">
-        <v>1790.605</v>
+        <v>1853.074</v>
       </c>
       <c r="F47">
-        <v>2811.105</v>
+        <v>2873.574</v>
       </c>
       <c r="G47">
         <v>249.1</v>
@@ -5147,28 +5147,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M47">
-        <v>152.6430015</v>
+        <v>156.0350682</v>
       </c>
       <c r="N47">
-        <v>553.1569985000001</v>
+        <v>549.7649318000001</v>
       </c>
       <c r="O47">
-        <v>165.94709955</v>
+        <v>164.92947954</v>
       </c>
       <c r="P47">
-        <v>387.2098989500001</v>
+        <v>384.8354522600001</v>
       </c>
       <c r="Q47">
-        <v>764.3098989500002</v>
+        <v>761.9354522600001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1497554425833521</v>
+        <v>0.1513133276145734</v>
       </c>
       <c r="T47">
-        <v>1.512678355442141</v>
+        <v>1.535347480871588</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.623860858763315</v>
+        <v>4.523342144442374</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09919379691186964</v>
+        <v>0.09891760040289561</v>
       </c>
       <c r="C48">
-        <v>4580.855357923036</v>
+        <v>4555.852034075038</v>
       </c>
       <c r="D48">
-        <v>7205.329357923035</v>
+        <v>7242.795034075038</v>
       </c>
       <c r="E48">
-        <v>1853.074</v>
+        <v>1915.543</v>
       </c>
       <c r="F48">
-        <v>2873.574</v>
+        <v>2936.043</v>
       </c>
       <c r="G48">
         <v>249.1</v>
@@ -5229,28 +5229,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M48">
-        <v>156.0350682</v>
+        <v>159.4271349</v>
       </c>
       <c r="N48">
-        <v>549.7649318000001</v>
+        <v>546.3728651000001</v>
       </c>
       <c r="O48">
-        <v>164.92947954</v>
+        <v>163.91185953</v>
       </c>
       <c r="P48">
-        <v>384.8354522600001</v>
+        <v>382.4610055700001</v>
       </c>
       <c r="Q48">
-        <v>761.9354522600001</v>
+        <v>759.5610055700001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1513133276145734</v>
+        <v>0.1529300007601804</v>
       </c>
       <c r="T48">
-        <v>1.535347480871588</v>
+        <v>1.558872044996487</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.523342144442374</v>
+        <v>4.427100822220196</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09891760040289561</v>
+        <v>0.09864140389392159</v>
       </c>
       <c r="C49">
-        <v>4555.852034075038</v>
+        <v>4531.240368593282</v>
       </c>
       <c r="D49">
-        <v>7242.795034075038</v>
+        <v>7280.652368593283</v>
       </c>
       <c r="E49">
-        <v>1915.543</v>
+        <v>1978.012</v>
       </c>
       <c r="F49">
-        <v>2936.043</v>
+        <v>2998.512</v>
       </c>
       <c r="G49">
         <v>249.1</v>
@@ -5311,28 +5311,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M49">
-        <v>159.4271349</v>
+        <v>162.8192016</v>
       </c>
       <c r="N49">
-        <v>546.3728651000001</v>
+        <v>542.9807984</v>
       </c>
       <c r="O49">
-        <v>163.91185953</v>
+        <v>162.89423952</v>
       </c>
       <c r="P49">
-        <v>382.4610055700001</v>
+        <v>380.08655888</v>
       </c>
       <c r="Q49">
-        <v>759.5610055700001</v>
+        <v>757.18655888</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1529300007601804</v>
+        <v>0.1546088536421569</v>
       </c>
       <c r="T49">
-        <v>1.558872044996487</v>
+        <v>1.583301400049266</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.427100822220196</v>
+        <v>4.334869555090608</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09864140389392159</v>
+        <v>0.09870820738494757</v>
       </c>
       <c r="C50">
-        <v>4531.240368593283</v>
+        <v>4459.57859833687</v>
       </c>
       <c r="D50">
-        <v>7280.652368593283</v>
+        <v>7271.459598336869</v>
       </c>
       <c r="E50">
-        <v>1978.012</v>
+        <v>2040.481</v>
       </c>
       <c r="F50">
-        <v>2998.512</v>
+        <v>3060.981</v>
       </c>
       <c r="G50">
         <v>249.1</v>
@@ -5393,45 +5393,45 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M50">
-        <v>162.8192016</v>
+        <v>169.2722493</v>
       </c>
       <c r="N50">
-        <v>542.9807984000001</v>
+        <v>536.5277507000001</v>
       </c>
       <c r="O50">
-        <v>162.89423952</v>
+        <v>160.95832521</v>
       </c>
       <c r="P50">
-        <v>380.0865588800001</v>
+        <v>375.5694254900001</v>
       </c>
       <c r="Q50">
-        <v>757.1865588800001</v>
+        <v>752.6694254900001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1546088536421569</v>
+        <v>0.1563535438920541</v>
       </c>
       <c r="T50">
-        <v>1.583301400049266</v>
+        <v>1.608688769025683</v>
       </c>
       <c r="U50">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V50">
         <v>0.3</v>
       </c>
       <c r="W50">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.334869555090609</v>
+        <v>4.169614351547463</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09870820738494757</v>
+        <v>0.09843901087597354</v>
       </c>
       <c r="C51">
-        <v>4459.57859833687</v>
+        <v>4434.295926621609</v>
       </c>
       <c r="D51">
-        <v>7271.459598336869</v>
+        <v>7308.645926621609</v>
       </c>
       <c r="E51">
-        <v>2040.481</v>
+        <v>2102.95</v>
       </c>
       <c r="F51">
-        <v>3060.981</v>
+        <v>3123.45</v>
       </c>
       <c r="G51">
         <v>249.1</v>
@@ -5475,28 +5475,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M51">
-        <v>169.2722493</v>
+        <v>172.726785</v>
       </c>
       <c r="N51">
-        <v>536.5277507000001</v>
+        <v>533.0732150000001</v>
       </c>
       <c r="O51">
-        <v>160.95832521</v>
+        <v>159.9219645</v>
       </c>
       <c r="P51">
-        <v>375.5694254900001</v>
+        <v>373.1512505000001</v>
       </c>
       <c r="Q51">
-        <v>752.6694254900001</v>
+        <v>750.2512505000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1563535438920541</v>
+        <v>0.1581680217519471</v>
       </c>
       <c r="T51">
-        <v>1.608688769025683</v>
+        <v>1.635091632761158</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.169614351547463</v>
+        <v>4.086222064516514</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09843901087597354</v>
+        <v>0.09816981436699952</v>
       </c>
       <c r="C52">
-        <v>4434.295926621609</v>
+        <v>4409.395552605005</v>
       </c>
       <c r="D52">
-        <v>7308.645926621609</v>
+        <v>7346.214552605004</v>
       </c>
       <c r="E52">
-        <v>2102.95</v>
+        <v>2165.419</v>
       </c>
       <c r="F52">
-        <v>3123.45</v>
+        <v>3185.919</v>
       </c>
       <c r="G52">
         <v>249.1</v>
@@ -5557,28 +5557,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M52">
-        <v>172.726785</v>
+        <v>176.1813207</v>
       </c>
       <c r="N52">
-        <v>533.0732150000001</v>
+        <v>529.6186793000001</v>
       </c>
       <c r="O52">
-        <v>159.9219645</v>
+        <v>158.88560379</v>
       </c>
       <c r="P52">
-        <v>373.1512505000001</v>
+        <v>370.73307551</v>
       </c>
       <c r="Q52">
-        <v>750.2512505000001</v>
+        <v>747.8330755100001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1581680217519471</v>
+        <v>0.1600565599326521</v>
       </c>
       <c r="T52">
-        <v>1.635091632761158</v>
+        <v>1.662572164404203</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.086222064516514</v>
+        <v>4.006100063251484</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09816981436699952</v>
+        <v>0.09790061785802549</v>
       </c>
       <c r="C53">
-        <v>4409.395552605005</v>
+        <v>4384.883402121155</v>
       </c>
       <c r="D53">
-        <v>7346.214552605004</v>
+        <v>7384.171402121155</v>
       </c>
       <c r="E53">
-        <v>2165.419</v>
+        <v>2227.888</v>
       </c>
       <c r="F53">
-        <v>3185.919</v>
+        <v>3248.388</v>
       </c>
       <c r="G53">
         <v>249.1</v>
@@ -5639,28 +5639,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M53">
-        <v>176.1813207</v>
+        <v>179.6358564</v>
       </c>
       <c r="N53">
-        <v>529.6186793000001</v>
+        <v>526.1641436000001</v>
       </c>
       <c r="O53">
-        <v>158.88560379</v>
+        <v>157.84924308</v>
       </c>
       <c r="P53">
-        <v>370.73307551</v>
+        <v>368.31490052</v>
       </c>
       <c r="Q53">
-        <v>747.8330755100001</v>
+        <v>745.4149005200001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1600565599326521</v>
+        <v>0.1620237872042198</v>
       </c>
       <c r="T53">
-        <v>1.662572164404203</v>
+        <v>1.691197718199041</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.006100063251484</v>
+        <v>3.929059677419725</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09790061785802549</v>
+        <v>0.09763142134905146</v>
       </c>
       <c r="C54">
-        <v>4384.883402121155</v>
+        <v>4360.765524112009</v>
       </c>
       <c r="D54">
-        <v>7384.171402121155</v>
+        <v>7422.522524112009</v>
       </c>
       <c r="E54">
-        <v>2227.888</v>
+        <v>2290.357</v>
       </c>
       <c r="F54">
-        <v>3248.388</v>
+        <v>3310.857</v>
       </c>
       <c r="G54">
         <v>249.1</v>
@@ -5721,28 +5721,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M54">
-        <v>179.6358564</v>
+        <v>183.0903921</v>
       </c>
       <c r="N54">
-        <v>526.1641436000001</v>
+        <v>522.7096079</v>
       </c>
       <c r="O54">
-        <v>157.84924308</v>
+        <v>156.81288237</v>
       </c>
       <c r="P54">
-        <v>368.31490052</v>
+        <v>365.89672553</v>
       </c>
       <c r="Q54">
-        <v>745.4149005200001</v>
+        <v>742.99672553</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1620237872042198</v>
+        <v>0.1640747262745776</v>
       </c>
       <c r="T54">
-        <v>1.691197718199041</v>
+        <v>1.721041380666</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.929059677419725</v>
+        <v>3.854926475958975</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09763142134905146</v>
+        <v>0.09736222484007745</v>
       </c>
       <c r="C55">
-        <v>4360.765524112009</v>
+        <v>4337.048093840996</v>
       </c>
       <c r="D55">
-        <v>7422.522524112009</v>
+        <v>7461.274093840996</v>
       </c>
       <c r="E55">
-        <v>2290.357</v>
+        <v>2352.826</v>
       </c>
       <c r="F55">
-        <v>3310.857</v>
+        <v>3373.326</v>
       </c>
       <c r="G55">
         <v>249.1</v>
@@ -5803,28 +5803,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M55">
-        <v>183.0903921</v>
+        <v>186.5449278</v>
       </c>
       <c r="N55">
-        <v>522.7096079</v>
+        <v>519.2550722000001</v>
       </c>
       <c r="O55">
-        <v>156.81288237</v>
+        <v>155.77652166</v>
       </c>
       <c r="P55">
-        <v>365.89672553</v>
+        <v>363.4785505400001</v>
       </c>
       <c r="Q55">
-        <v>742.99672553</v>
+        <v>740.5785505400002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1640747262745776</v>
+        <v>0.166214836608864</v>
       </c>
       <c r="T55">
-        <v>1.721041380666</v>
+        <v>1.752182593675</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.854926475958975</v>
+        <v>3.783538948626402</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09736222484007745</v>
+        <v>0.09709302833110342</v>
       </c>
       <c r="C56">
-        <v>4337.048093840996</v>
+        <v>4313.737416207827</v>
       </c>
       <c r="D56">
-        <v>7461.274093840996</v>
+        <v>7500.432416207826</v>
       </c>
       <c r="E56">
-        <v>2352.826</v>
+        <v>2415.295</v>
       </c>
       <c r="F56">
-        <v>3373.326</v>
+        <v>3435.795</v>
       </c>
       <c r="G56">
         <v>249.1</v>
@@ -5885,28 +5885,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M56">
-        <v>186.5449278</v>
+        <v>189.9994635</v>
       </c>
       <c r="N56">
-        <v>519.2550722000001</v>
+        <v>515.8005365</v>
       </c>
       <c r="O56">
-        <v>155.77652166</v>
+        <v>154.74016095</v>
       </c>
       <c r="P56">
-        <v>363.4785505400001</v>
+        <v>361.06037555</v>
       </c>
       <c r="Q56">
-        <v>740.5785505400002</v>
+        <v>738.16037555</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.166214836608864</v>
+        <v>0.1684500629580076</v>
       </c>
       <c r="T56">
-        <v>1.752182593675</v>
+        <v>1.784707860595512</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.783538948626402</v>
+        <v>3.714747331378649</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09709302833110342</v>
+        <v>0.09682383182212941</v>
       </c>
       <c r="C57">
-        <v>4313.737416207827</v>
+        <v>4290.839929168229</v>
       </c>
       <c r="D57">
-        <v>7500.432416207826</v>
+        <v>7540.003929168229</v>
       </c>
       <c r="E57">
-        <v>2415.295</v>
+        <v>2477.764</v>
       </c>
       <c r="F57">
-        <v>3435.795</v>
+        <v>3498.264</v>
       </c>
       <c r="G57">
         <v>249.1</v>
@@ -5967,28 +5967,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M57">
-        <v>189.9994635</v>
+        <v>193.4539992</v>
       </c>
       <c r="N57">
-        <v>515.8005365</v>
+        <v>512.3460008000001</v>
       </c>
       <c r="O57">
-        <v>154.74016095</v>
+        <v>153.70380024</v>
       </c>
       <c r="P57">
-        <v>361.06037555</v>
+        <v>358.64220056</v>
       </c>
       <c r="Q57">
-        <v>738.16037555</v>
+        <v>735.7422005600001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1684500629580076</v>
+        <v>0.1707868905048396</v>
       </c>
       <c r="T57">
-        <v>1.784707860595512</v>
+        <v>1.818711548739684</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.714747331378649</v>
+        <v>3.64841255760403</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09682383182212941</v>
+        <v>0.09655463531315538</v>
       </c>
       <c r="C58">
-        <v>4290.839929168229</v>
+        <v>4268.362207262516</v>
       </c>
       <c r="D58">
-        <v>7540.003929168229</v>
+        <v>7579.995207262516</v>
       </c>
       <c r="E58">
-        <v>2477.764</v>
+        <v>2540.233</v>
       </c>
       <c r="F58">
-        <v>3498.264</v>
+        <v>3560.733</v>
       </c>
       <c r="G58">
         <v>249.1</v>
@@ -6049,28 +6049,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M58">
-        <v>193.4539992</v>
+        <v>196.9085349</v>
       </c>
       <c r="N58">
-        <v>512.3460008000001</v>
+        <v>508.8914651000001</v>
       </c>
       <c r="O58">
-        <v>153.70380024</v>
+        <v>152.66743953</v>
       </c>
       <c r="P58">
-        <v>358.64220056</v>
+        <v>356.22402557</v>
       </c>
       <c r="Q58">
-        <v>735.7422005600001</v>
+        <v>733.32402557</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1707868905048396</v>
+        <v>0.1732324077050125</v>
       </c>
       <c r="T58">
-        <v>1.818711548739684</v>
+        <v>1.854296803774282</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.64841255760403</v>
+        <v>3.584405319751328</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09655463531315538</v>
+        <v>0.09628543880418136</v>
       </c>
       <c r="C59">
-        <v>4268.362207262516</v>
+        <v>4246.31096525704</v>
       </c>
       <c r="D59">
-        <v>7579.995207262516</v>
+        <v>7620.41296525704</v>
       </c>
       <c r="E59">
-        <v>2540.233</v>
+        <v>2602.702</v>
       </c>
       <c r="F59">
-        <v>3560.733</v>
+        <v>3623.202</v>
       </c>
       <c r="G59">
         <v>249.1</v>
@@ -6131,28 +6131,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M59">
-        <v>196.9085349</v>
+        <v>200.3630706</v>
       </c>
       <c r="N59">
-        <v>508.8914651000001</v>
+        <v>505.4369294000001</v>
       </c>
       <c r="O59">
-        <v>152.66743953</v>
+        <v>151.63107882</v>
       </c>
       <c r="P59">
-        <v>356.22402557</v>
+        <v>353.8058505800001</v>
       </c>
       <c r="Q59">
-        <v>733.32402557</v>
+        <v>730.9058505800001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1732324077050125</v>
+        <v>0.1757943781051937</v>
       </c>
       <c r="T59">
-        <v>1.854296803774282</v>
+        <v>1.891576594762908</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.584405319751328</v>
+        <v>3.522605228031477</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09628543880418133</v>
+        <v>0.09601624229520732</v>
       </c>
       <c r="C60">
-        <v>4246.310965257047</v>
+        <v>4224.693061902789</v>
       </c>
       <c r="D60">
-        <v>7620.412965257045</v>
+        <v>7661.264061902788</v>
       </c>
       <c r="E60">
-        <v>2602.701999999999</v>
+        <v>2665.170999999999</v>
       </c>
       <c r="F60">
-        <v>3623.201999999999</v>
+        <v>3685.670999999999</v>
       </c>
       <c r="G60">
         <v>249.1</v>
@@ -6213,28 +6213,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M60">
-        <v>200.3630706</v>
+        <v>203.8176063</v>
       </c>
       <c r="N60">
-        <v>505.4369294000001</v>
+        <v>501.9823937000001</v>
       </c>
       <c r="O60">
-        <v>151.63107882</v>
+        <v>150.59471811</v>
       </c>
       <c r="P60">
-        <v>353.8058505800001</v>
+        <v>351.3876755900001</v>
       </c>
       <c r="Q60">
-        <v>730.9058505800001</v>
+        <v>728.4876755900001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1757943781051937</v>
+        <v>0.1784813226712374</v>
       </c>
       <c r="T60">
-        <v>1.891576594762908</v>
+        <v>1.930674912141223</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.522605228031479</v>
+        <v>3.462900054675012</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09601624229520732</v>
+        <v>0.0957470457862333</v>
       </c>
       <c r="C61">
-        <v>4224.693061902789</v>
+        <v>4203.515503815471</v>
       </c>
       <c r="D61">
-        <v>7661.264061902788</v>
+        <v>7702.55550381547</v>
       </c>
       <c r="E61">
-        <v>2665.170999999999</v>
+        <v>2727.639999999999</v>
       </c>
       <c r="F61">
-        <v>3685.670999999999</v>
+        <v>3748.139999999999</v>
       </c>
       <c r="G61">
         <v>249.1</v>
@@ -6295,28 +6295,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M61">
-        <v>203.8176063</v>
+        <v>207.272142</v>
       </c>
       <c r="N61">
-        <v>501.9823937000001</v>
+        <v>498.5278580000001</v>
       </c>
       <c r="O61">
-        <v>150.59471811</v>
+        <v>149.5583574</v>
       </c>
       <c r="P61">
-        <v>351.3876755900001</v>
+        <v>348.9695006000001</v>
       </c>
       <c r="Q61">
-        <v>728.4876755900001</v>
+        <v>726.0695006000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1784813226712374</v>
+        <v>0.1813026144655833</v>
       </c>
       <c r="T61">
-        <v>1.930674912141223</v>
+        <v>1.971728145388455</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.462900054675012</v>
+        <v>3.405185053763762</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0957470457862333</v>
+        <v>0.09547784927725927</v>
       </c>
       <c r="C62">
-        <v>4203.515503815471</v>
+        <v>4182.785449481843</v>
       </c>
       <c r="D62">
-        <v>7702.55550381547</v>
+        <v>7744.294449481842</v>
       </c>
       <c r="E62">
-        <v>2727.639999999999</v>
+        <v>2790.108999999999</v>
       </c>
       <c r="F62">
-        <v>3748.139999999999</v>
+        <v>3810.608999999999</v>
       </c>
       <c r="G62">
         <v>249.1</v>
@@ -6377,28 +6377,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M62">
-        <v>207.272142</v>
+        <v>210.7266777</v>
       </c>
       <c r="N62">
-        <v>498.5278580000001</v>
+        <v>495.0733223000001</v>
       </c>
       <c r="O62">
-        <v>149.5583574</v>
+        <v>148.52199669</v>
       </c>
       <c r="P62">
-        <v>348.9695006000001</v>
+        <v>346.55132561</v>
       </c>
       <c r="Q62">
-        <v>726.0695006000001</v>
+        <v>723.6513256100001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1813026144655833</v>
+        <v>0.1842685878904084</v>
       </c>
       <c r="T62">
-        <v>1.971728145388455</v>
+        <v>2.014886672648365</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.405185053763762</v>
+        <v>3.349362347964356</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09547784927725927</v>
+        <v>0.09520865276828525</v>
       </c>
       <c r="C63">
-        <v>4182.785449481843</v>
+        <v>4162.510213396929</v>
       </c>
       <c r="D63">
-        <v>7744.294449481842</v>
+        <v>7786.488213396928</v>
       </c>
       <c r="E63">
-        <v>2790.108999999999</v>
+        <v>2852.578</v>
       </c>
       <c r="F63">
-        <v>3810.608999999999</v>
+        <v>3873.078</v>
       </c>
       <c r="G63">
         <v>249.1</v>
@@ -6459,28 +6459,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M63">
-        <v>210.7266777</v>
+        <v>214.1812134</v>
       </c>
       <c r="N63">
-        <v>495.0733223000001</v>
+        <v>491.6187866000001</v>
       </c>
       <c r="O63">
-        <v>148.52199669</v>
+        <v>147.48563598</v>
       </c>
       <c r="P63">
-        <v>346.55132561</v>
+        <v>344.13315062</v>
       </c>
       <c r="Q63">
-        <v>723.6513256100001</v>
+        <v>721.2331506200001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1842685878904084</v>
+        <v>0.187390665179698</v>
       </c>
       <c r="T63">
-        <v>2.014886672648365</v>
+        <v>2.060316701343007</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.349362347964356</v>
+        <v>3.295340374610092</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09520865276828525</v>
+        <v>0.09493945625931124</v>
       </c>
       <c r="C64">
-        <v>4162.510213396929</v>
+        <v>4142.69727033725</v>
       </c>
       <c r="D64">
-        <v>7786.488213396928</v>
+        <v>7829.14427033725</v>
       </c>
       <c r="E64">
-        <v>2852.578</v>
+        <v>2915.047</v>
       </c>
       <c r="F64">
-        <v>3873.078</v>
+        <v>3935.547</v>
       </c>
       <c r="G64">
         <v>249.1</v>
@@ -6541,28 +6541,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M64">
-        <v>214.1812134</v>
+        <v>217.6357491</v>
       </c>
       <c r="N64">
-        <v>491.6187866000001</v>
+        <v>488.1642509000001</v>
       </c>
       <c r="O64">
-        <v>147.48563598</v>
+        <v>146.44927527</v>
       </c>
       <c r="P64">
-        <v>344.13315062</v>
+        <v>341.71497563</v>
       </c>
       <c r="Q64">
-        <v>721.2331506200001</v>
+        <v>718.81497563</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.187390665179698</v>
+        <v>0.1906815034035439</v>
       </c>
       <c r="T64">
-        <v>2.060316701343007</v>
+        <v>2.108202407264387</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.295340374610092</v>
+        <v>3.243033384536916</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09493945625931124</v>
+        <v>0.09467025975033722</v>
       </c>
       <c r="C65">
-        <v>4142.69727033725</v>
+        <v>4123.354259775322</v>
       </c>
       <c r="D65">
-        <v>7829.14427033725</v>
+        <v>7872.270259775321</v>
       </c>
       <c r="E65">
-        <v>2915.047</v>
+        <v>2977.516</v>
       </c>
       <c r="F65">
-        <v>3935.547</v>
+        <v>3998.016</v>
       </c>
       <c r="G65">
         <v>249.1</v>
@@ -6623,28 +6623,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M65">
-        <v>217.6357491</v>
+        <v>221.0902848</v>
       </c>
       <c r="N65">
-        <v>488.1642509000001</v>
+        <v>484.7097152000001</v>
       </c>
       <c r="O65">
-        <v>146.44927527</v>
+        <v>145.41291456</v>
       </c>
       <c r="P65">
-        <v>341.71497563</v>
+        <v>339.29680064</v>
       </c>
       <c r="Q65">
-        <v>718.81497563</v>
+        <v>716.39680064</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1906815034035439</v>
+        <v>0.1941551659731589</v>
       </c>
       <c r="T65">
-        <v>2.108202407264387</v>
+        <v>2.158748430181398</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.243033384536916</v>
+        <v>3.192360987903526</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09467025975033722</v>
+        <v>0.09440106324136317</v>
       </c>
       <c r="C66">
-        <v>4123.354259775322</v>
+        <v>4104.488990440788</v>
       </c>
       <c r="D66">
-        <v>7872.270259775321</v>
+        <v>7915.873990440788</v>
       </c>
       <c r="E66">
-        <v>2977.516</v>
+        <v>3039.985</v>
       </c>
       <c r="F66">
-        <v>3998.016</v>
+        <v>4060.485</v>
       </c>
       <c r="G66">
         <v>249.1</v>
@@ -6705,28 +6705,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M66">
-        <v>221.0902848</v>
+        <v>224.5448205</v>
       </c>
       <c r="N66">
-        <v>484.7097152000001</v>
+        <v>481.2551795000001</v>
       </c>
       <c r="O66">
-        <v>145.41291456</v>
+        <v>144.37655385</v>
       </c>
       <c r="P66">
-        <v>339.29680064</v>
+        <v>336.87862565</v>
       </c>
       <c r="Q66">
-        <v>716.39680064</v>
+        <v>713.97862565</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1941551659731589</v>
+        <v>0.1978273235467519</v>
       </c>
       <c r="T66">
-        <v>2.158748430181398</v>
+        <v>2.212182797265096</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.192360987903526</v>
+        <v>3.14324774193578</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09440106324136317</v>
+        <v>0.09413186673238916</v>
       </c>
       <c r="C67">
-        <v>4104.488990440788</v>
+        <v>4086.109445034042</v>
       </c>
       <c r="D67">
-        <v>7915.873990440788</v>
+        <v>7959.963445034042</v>
       </c>
       <c r="E67">
-        <v>3039.985</v>
+        <v>3102.454</v>
       </c>
       <c r="F67">
-        <v>4060.485</v>
+        <v>4122.954</v>
       </c>
       <c r="G67">
         <v>249.1</v>
@@ -6787,28 +6787,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M67">
-        <v>224.5448205</v>
+        <v>227.9993562</v>
       </c>
       <c r="N67">
-        <v>481.2551795000001</v>
+        <v>477.8006438000001</v>
       </c>
       <c r="O67">
-        <v>144.37655385</v>
+        <v>143.34019314</v>
       </c>
       <c r="P67">
-        <v>336.87862565</v>
+        <v>334.4604506600001</v>
       </c>
       <c r="Q67">
-        <v>713.97862565</v>
+        <v>711.5604506600001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1978273235467519</v>
+        <v>0.2017154903893799</v>
       </c>
       <c r="T67">
-        <v>2.212182797265096</v>
+        <v>2.268760362412541</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.14324774193578</v>
+        <v>3.095622776148875</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09413186673238916</v>
+        <v>0.09386267022341513</v>
       </c>
       <c r="C68">
-        <v>4086.109445034042</v>
+        <v>4068.223785098241</v>
       </c>
       <c r="D68">
-        <v>7959.963445034042</v>
+        <v>8004.546785098241</v>
       </c>
       <c r="E68">
-        <v>3102.454</v>
+        <v>3164.923</v>
       </c>
       <c r="F68">
-        <v>4122.954</v>
+        <v>4185.423</v>
       </c>
       <c r="G68">
         <v>249.1</v>
@@ -6869,28 +6869,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M68">
-        <v>227.9993562</v>
+        <v>231.4538919</v>
       </c>
       <c r="N68">
-        <v>477.8006438000001</v>
+        <v>474.3461081</v>
       </c>
       <c r="O68">
-        <v>143.34019314</v>
+        <v>142.30383243</v>
       </c>
       <c r="P68">
-        <v>334.4604506600001</v>
+        <v>332.04227567</v>
       </c>
       <c r="Q68">
-        <v>711.5604506600001</v>
+        <v>709.1422756700001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2017154903893799</v>
+        <v>0.2058393037073186</v>
       </c>
       <c r="T68">
-        <v>2.268760362412541</v>
+        <v>2.328766870902255</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.095622776148875</v>
+        <v>3.049419451131727</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09386267022341513</v>
+        <v>0.09359347371444111</v>
       </c>
       <c r="C69">
-        <v>4068.223785098241</v>
+        <v>4050.840356055947</v>
       </c>
       <c r="D69">
-        <v>8004.546785098241</v>
+        <v>8049.632356055947</v>
       </c>
       <c r="E69">
-        <v>3164.923</v>
+        <v>3227.392</v>
       </c>
       <c r="F69">
-        <v>4185.423</v>
+        <v>4247.892</v>
       </c>
       <c r="G69">
         <v>249.1</v>
@@ -6951,28 +6951,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M69">
-        <v>231.4538919</v>
+        <v>234.9084276</v>
       </c>
       <c r="N69">
-        <v>474.3461081</v>
+        <v>470.8915724000001</v>
       </c>
       <c r="O69">
-        <v>142.30383243</v>
+        <v>141.26747172</v>
       </c>
       <c r="P69">
-        <v>332.04227567</v>
+        <v>329.6241006800001</v>
       </c>
       <c r="Q69">
-        <v>709.1422756700001</v>
+        <v>706.7241006800001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2058393037073186</v>
+        <v>0.2102208553576285</v>
       </c>
       <c r="T69">
-        <v>2.328766870902255</v>
+        <v>2.392523786172577</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.049419451131727</v>
+        <v>3.004575047438613</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09359347371444111</v>
+        <v>0.09453177720546709</v>
       </c>
       <c r="C70">
-        <v>4050.840356055947</v>
+        <v>3833.380124988848</v>
       </c>
       <c r="D70">
-        <v>8049.632356055947</v>
+        <v>7894.641124988848</v>
       </c>
       <c r="E70">
-        <v>3227.392</v>
+        <v>3289.861</v>
       </c>
       <c r="F70">
-        <v>4247.892</v>
+        <v>4310.361</v>
       </c>
       <c r="G70">
         <v>249.1</v>
@@ -7033,45 +7033,45 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M70">
-        <v>234.9084276</v>
+        <v>249.1388658</v>
       </c>
       <c r="N70">
-        <v>470.8915724000001</v>
+        <v>456.6611342</v>
       </c>
       <c r="O70">
-        <v>141.26747172</v>
+        <v>136.99834026</v>
       </c>
       <c r="P70">
-        <v>329.6241006800001</v>
+        <v>319.66279394</v>
       </c>
       <c r="Q70">
-        <v>706.7241006800001</v>
+        <v>696.7627939400001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2102208553576285</v>
+        <v>0.2148850877595713</v>
       </c>
       <c r="T70">
-        <v>2.392523786172577</v>
+        <v>2.460394050815177</v>
       </c>
       <c r="U70">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V70">
         <v>0.3</v>
       </c>
       <c r="W70">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>3.004575047438613</v>
+        <v>2.832958228872213</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09453177720546709</v>
+        <v>0.09428008069649306</v>
       </c>
       <c r="C71">
-        <v>3833.380124988848</v>
+        <v>3811.898136194592</v>
       </c>
       <c r="D71">
-        <v>7894.641124988848</v>
+        <v>7935.628136194591</v>
       </c>
       <c r="E71">
-        <v>3289.861</v>
+        <v>3352.33</v>
       </c>
       <c r="F71">
-        <v>4310.361</v>
+        <v>4372.83</v>
       </c>
       <c r="G71">
         <v>249.1</v>
@@ -7115,28 +7115,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M71">
-        <v>249.1388658</v>
+        <v>252.749574</v>
       </c>
       <c r="N71">
-        <v>456.6611342</v>
+        <v>453.050426</v>
       </c>
       <c r="O71">
-        <v>136.99834026</v>
+        <v>135.9151278</v>
       </c>
       <c r="P71">
-        <v>319.66279394</v>
+        <v>317.1352982</v>
       </c>
       <c r="Q71">
-        <v>696.7627939400001</v>
+        <v>694.2352982</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2148850877595713</v>
+        <v>0.2198602689883102</v>
       </c>
       <c r="T71">
-        <v>2.460394050815177</v>
+        <v>2.532788999767284</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.832958228872213</v>
+        <v>2.792487397031182</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09428008069649306</v>
+        <v>0.09402838418751903</v>
       </c>
       <c r="C72">
-        <v>3811.898136194592</v>
+        <v>3790.843957197719</v>
       </c>
       <c r="D72">
-        <v>7935.628136194591</v>
+        <v>7977.042957197719</v>
       </c>
       <c r="E72">
-        <v>3352.33</v>
+        <v>3414.799</v>
       </c>
       <c r="F72">
-        <v>4372.83</v>
+        <v>4435.299</v>
       </c>
       <c r="G72">
         <v>249.1</v>
@@ -7197,28 +7197,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M72">
-        <v>252.749574</v>
+        <v>256.3602822</v>
       </c>
       <c r="N72">
-        <v>453.050426</v>
+        <v>449.4397178</v>
       </c>
       <c r="O72">
-        <v>135.9151278</v>
+        <v>134.83191534</v>
       </c>
       <c r="P72">
-        <v>317.1352982</v>
+        <v>314.60780246</v>
       </c>
       <c r="Q72">
-        <v>694.2352982</v>
+        <v>691.70780246</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2198602689883102</v>
+        <v>0.2251785661638588</v>
       </c>
       <c r="T72">
-        <v>2.532788999767284</v>
+        <v>2.610176703819536</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.792487397031182</v>
+        <v>2.753156588622292</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09402838418751905</v>
+        <v>0.09377668767854502</v>
       </c>
       <c r="C73">
-        <v>3790.843957197718</v>
+        <v>3770.22432115788</v>
       </c>
       <c r="D73">
-        <v>7977.042957197717</v>
+        <v>8018.892321157879</v>
       </c>
       <c r="E73">
-        <v>3414.798999999999</v>
+        <v>3477.267999999999</v>
       </c>
       <c r="F73">
-        <v>4435.298999999999</v>
+        <v>4497.767999999999</v>
       </c>
       <c r="G73">
         <v>249.1</v>
@@ -7279,28 +7279,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M73">
-        <v>256.3602822</v>
+        <v>259.9709903999999</v>
       </c>
       <c r="N73">
-        <v>449.4397178000001</v>
+        <v>445.8290096000001</v>
       </c>
       <c r="O73">
-        <v>134.83191534</v>
+        <v>133.74870288</v>
       </c>
       <c r="P73">
-        <v>314.6078024600001</v>
+        <v>312.0803067200001</v>
       </c>
       <c r="Q73">
-        <v>691.70780246</v>
+        <v>689.1803067200001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2251785661638587</v>
+        <v>0.2308767417090893</v>
       </c>
       <c r="T73">
-        <v>2.610176703819536</v>
+        <v>2.693092101018378</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.753156588622292</v>
+        <v>2.714918302669205</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09377668767854502</v>
+        <v>0.093524991169571</v>
       </c>
       <c r="C74">
-        <v>3770.22432115788</v>
+        <v>3750.046103274586</v>
       </c>
       <c r="D74">
-        <v>8018.892321157879</v>
+        <v>8061.183103274586</v>
       </c>
       <c r="E74">
-        <v>3477.267999999999</v>
+        <v>3539.736999999999</v>
       </c>
       <c r="F74">
-        <v>4497.767999999999</v>
+        <v>4560.236999999999</v>
       </c>
       <c r="G74">
         <v>249.1</v>
@@ -7361,28 +7361,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M74">
-        <v>259.9709903999999</v>
+        <v>263.5816986</v>
       </c>
       <c r="N74">
-        <v>445.8290096000001</v>
+        <v>442.2183014000001</v>
       </c>
       <c r="O74">
-        <v>133.74870288</v>
+        <v>132.66549042</v>
       </c>
       <c r="P74">
-        <v>312.0803067200001</v>
+        <v>309.5528109800001</v>
       </c>
       <c r="Q74">
-        <v>689.1803067200001</v>
+        <v>686.6528109800001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2308767417090893</v>
+        <v>0.2369970043317444</v>
       </c>
       <c r="T74">
-        <v>2.693092101018378</v>
+        <v>2.782149379491207</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.714918302669205</v>
+        <v>2.677727640988805</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.093524991169571</v>
+        <v>0.09327329466059697</v>
       </c>
       <c r="C75">
-        <v>3750.046103274586</v>
+        <v>3730.316324552578</v>
       </c>
       <c r="D75">
-        <v>8061.183103274586</v>
+        <v>8103.922324552578</v>
       </c>
       <c r="E75">
-        <v>3539.736999999999</v>
+        <v>3602.205999999999</v>
       </c>
       <c r="F75">
-        <v>4560.236999999999</v>
+        <v>4622.705999999999</v>
       </c>
       <c r="G75">
         <v>249.1</v>
@@ -7443,28 +7443,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M75">
-        <v>263.5816986</v>
+        <v>267.1924068</v>
       </c>
       <c r="N75">
-        <v>442.2183014000001</v>
+        <v>438.6075932000001</v>
       </c>
       <c r="O75">
-        <v>132.66549042</v>
+        <v>131.58227796</v>
       </c>
       <c r="P75">
-        <v>309.5528109800001</v>
+        <v>307.0253152400001</v>
       </c>
       <c r="Q75">
-        <v>686.6528109800001</v>
+        <v>684.1253152400001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2369970043317444</v>
+        <v>0.2435880563869114</v>
       </c>
       <c r="T75">
-        <v>2.782149379491207</v>
+        <v>2.878057217846563</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.677727640988805</v>
+        <v>2.641542132326794</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09327329466059697</v>
+        <v>0.09302159815162292</v>
       </c>
       <c r="C76">
-        <v>3730.316324552578</v>
+        <v>3711.042155687634</v>
       </c>
       <c r="D76">
-        <v>8103.922324552578</v>
+        <v>8147.117155687633</v>
       </c>
       <c r="E76">
-        <v>3602.205999999999</v>
+        <v>3664.674999999999</v>
       </c>
       <c r="F76">
-        <v>4622.705999999999</v>
+        <v>4685.174999999999</v>
       </c>
       <c r="G76">
         <v>249.1</v>
@@ -7525,28 +7525,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M76">
-        <v>267.1924068</v>
+        <v>270.803115</v>
       </c>
       <c r="N76">
-        <v>438.6075932000001</v>
+        <v>434.9968850000001</v>
       </c>
       <c r="O76">
-        <v>131.58227796</v>
+        <v>130.4990655</v>
       </c>
       <c r="P76">
-        <v>307.0253152400001</v>
+        <v>304.4978195</v>
       </c>
       <c r="Q76">
-        <v>684.1253152400001</v>
+        <v>681.5978195</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2435880563869114</v>
+        <v>0.2507063926064917</v>
       </c>
       <c r="T76">
-        <v>2.878057217846563</v>
+        <v>2.981637683270346</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.641542132326794</v>
+        <v>2.606321570562437</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09302159815162292</v>
+        <v>0.09276990164264892</v>
       </c>
       <c r="C77">
-        <v>3711.042155687634</v>
+        <v>3692.230921077264</v>
       </c>
       <c r="D77">
-        <v>8147.117155687633</v>
+        <v>8190.774921077264</v>
       </c>
       <c r="E77">
-        <v>3664.674999999999</v>
+        <v>3727.144</v>
       </c>
       <c r="F77">
-        <v>4685.174999999999</v>
+        <v>4747.644</v>
       </c>
       <c r="G77">
         <v>249.1</v>
@@ -7607,28 +7607,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M77">
-        <v>270.803115</v>
+        <v>274.4138232</v>
       </c>
       <c r="N77">
-        <v>434.9968850000001</v>
+        <v>431.3861768</v>
       </c>
       <c r="O77">
-        <v>130.4990655</v>
+        <v>129.41585304</v>
       </c>
       <c r="P77">
-        <v>304.4978195</v>
+        <v>301.97032376</v>
       </c>
       <c r="Q77">
-        <v>681.5978195</v>
+        <v>679.0703237600001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2507063926064917</v>
+        <v>0.2584179235110372</v>
       </c>
       <c r="T77">
-        <v>2.981637683270346</v>
+        <v>3.093849854146113</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.606321570562437</v>
+        <v>2.572027865686615</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09276990164264892</v>
+        <v>0.0925182051336749</v>
       </c>
       <c r="C78">
-        <v>3692.230921077264</v>
+        <v>3673.890102961142</v>
       </c>
       <c r="D78">
-        <v>8190.774921077264</v>
+        <v>8234.903102961141</v>
       </c>
       <c r="E78">
-        <v>3727.144</v>
+        <v>3789.613</v>
       </c>
       <c r="F78">
-        <v>4747.644</v>
+        <v>4810.113</v>
       </c>
       <c r="G78">
         <v>249.1</v>
@@ -7689,28 +7689,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M78">
-        <v>274.4138232</v>
+        <v>278.0245314000001</v>
       </c>
       <c r="N78">
-        <v>431.3861768</v>
+        <v>427.7754686</v>
       </c>
       <c r="O78">
-        <v>129.41585304</v>
+        <v>128.33264058</v>
       </c>
       <c r="P78">
-        <v>301.97032376</v>
+        <v>299.44282802</v>
       </c>
       <c r="Q78">
-        <v>679.0703237600001</v>
+        <v>676.54282802</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2584179235110372</v>
+        <v>0.2668000223203256</v>
       </c>
       <c r="T78">
-        <v>3.093849854146113</v>
+        <v>3.215819605098032</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.572027865686615</v>
+        <v>2.538624906391983</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0925182051336749</v>
+        <v>0.09226650862470086</v>
       </c>
       <c r="C79">
-        <v>3673.890102961142</v>
+        <v>3656.027345696</v>
       </c>
       <c r="D79">
-        <v>8234.903102961141</v>
+        <v>8279.509345696</v>
       </c>
       <c r="E79">
-        <v>3789.613</v>
+        <v>3852.082</v>
       </c>
       <c r="F79">
-        <v>4810.113</v>
+        <v>4872.582</v>
       </c>
       <c r="G79">
         <v>249.1</v>
@@ -7771,28 +7771,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M79">
-        <v>278.0245314000001</v>
+        <v>281.6352396</v>
       </c>
       <c r="N79">
-        <v>427.7754686</v>
+        <v>424.1647604</v>
       </c>
       <c r="O79">
-        <v>128.33264058</v>
+        <v>127.24942812</v>
       </c>
       <c r="P79">
-        <v>299.44282802</v>
+        <v>296.91533228</v>
       </c>
       <c r="Q79">
-        <v>676.54282802</v>
+        <v>674.0153322800001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2668000223203256</v>
+        <v>0.2759441301122766</v>
       </c>
       <c r="T79">
-        <v>3.215819605098032</v>
+        <v>3.348877515227398</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.538624906391983</v>
+        <v>2.506078433233112</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09226650862470086</v>
+        <v>0.09395031211572683</v>
       </c>
       <c r="C80">
-        <v>3656.027345696</v>
+        <v>3304.026126117477</v>
       </c>
       <c r="D80">
-        <v>8279.509345696</v>
+        <v>7989.977126117477</v>
       </c>
       <c r="E80">
-        <v>3852.082</v>
+        <v>3914.551</v>
       </c>
       <c r="F80">
-        <v>4872.582</v>
+        <v>4935.051</v>
       </c>
       <c r="G80">
         <v>249.1</v>
@@ -7853,45 +7853,45 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M80">
-        <v>281.6352396</v>
+        <v>302.5186263000001</v>
       </c>
       <c r="N80">
-        <v>424.1647604</v>
+        <v>403.2813737</v>
       </c>
       <c r="O80">
-        <v>127.24942812</v>
+        <v>120.98441211</v>
       </c>
       <c r="P80">
-        <v>296.91533228</v>
+        <v>282.29696159</v>
       </c>
       <c r="Q80">
-        <v>674.0153322800001</v>
+        <v>659.39696159</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2759441301122766</v>
+        <v>0.285959105312985</v>
       </c>
       <c r="T80">
-        <v>3.348877515227398</v>
+        <v>3.494607607273847</v>
       </c>
       <c r="U80">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V80">
         <v>0.3</v>
       </c>
       <c r="W80">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y80">
-        <v>2.506078433233112</v>
+        <v>2.333079482187243</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09395031211572683</v>
+        <v>0.09372311560675281</v>
       </c>
       <c r="C81">
-        <v>3304.026126117477</v>
+        <v>3279.436443579472</v>
       </c>
       <c r="D81">
-        <v>7989.977126117477</v>
+        <v>8027.856443579473</v>
       </c>
       <c r="E81">
-        <v>3914.551</v>
+        <v>3977.02</v>
       </c>
       <c r="F81">
-        <v>4935.051</v>
+        <v>4997.52</v>
       </c>
       <c r="G81">
         <v>249.1</v>
@@ -7935,28 +7935,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M81">
-        <v>302.5186263000001</v>
+        <v>306.347976</v>
       </c>
       <c r="N81">
-        <v>403.2813737</v>
+        <v>399.4520240000001</v>
       </c>
       <c r="O81">
-        <v>120.98441211</v>
+        <v>119.8356072</v>
       </c>
       <c r="P81">
-        <v>282.29696159</v>
+        <v>279.6164168</v>
       </c>
       <c r="Q81">
-        <v>659.39696159</v>
+        <v>656.7164168</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.285959105312985</v>
+        <v>0.2969755780337641</v>
       </c>
       <c r="T81">
-        <v>3.494607607273847</v>
+        <v>3.654910708524941</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.333079482187243</v>
+        <v>2.303915988659902</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09372311560675281</v>
+        <v>0.09349591909777878</v>
       </c>
       <c r="C82">
-        <v>3279.436443579472</v>
+        <v>3255.207632531213</v>
       </c>
       <c r="D82">
-        <v>8027.856443579473</v>
+        <v>8066.096632531213</v>
       </c>
       <c r="E82">
-        <v>3977.02</v>
+        <v>4039.489</v>
       </c>
       <c r="F82">
-        <v>4997.52</v>
+        <v>5059.989</v>
       </c>
       <c r="G82">
         <v>249.1</v>
@@ -8017,28 +8017,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M82">
-        <v>306.347976</v>
+        <v>310.1773257</v>
       </c>
       <c r="N82">
-        <v>399.4520240000001</v>
+        <v>395.6226743</v>
       </c>
       <c r="O82">
-        <v>119.8356072</v>
+        <v>118.68680229</v>
       </c>
       <c r="P82">
-        <v>279.6164168</v>
+        <v>276.93587201</v>
       </c>
       <c r="Q82">
-        <v>656.7164168</v>
+        <v>654.03587201</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2969755780337641</v>
+        <v>0.3091516794619937</v>
       </c>
       <c r="T82">
-        <v>3.654910708524941</v>
+        <v>3.832087820434046</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.303915988659902</v>
+        <v>2.275472581392496</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09349591909777878</v>
+        <v>0.09487592258880476</v>
       </c>
       <c r="C83">
-        <v>3255.207632531213</v>
+        <v>2965.921877498161</v>
       </c>
       <c r="D83">
-        <v>8066.096632531213</v>
+        <v>7839.279877498161</v>
       </c>
       <c r="E83">
-        <v>4039.489</v>
+        <v>4101.958000000001</v>
       </c>
       <c r="F83">
-        <v>5059.989</v>
+        <v>5122.458000000001</v>
       </c>
       <c r="G83">
         <v>249.1</v>
@@ -8099,45 +8099,45 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M83">
-        <v>310.1773257</v>
+        <v>328.3495578000001</v>
       </c>
       <c r="N83">
-        <v>395.6226743</v>
+        <v>377.4504422</v>
       </c>
       <c r="O83">
-        <v>118.68680229</v>
+        <v>113.23513266</v>
       </c>
       <c r="P83">
-        <v>276.93587201</v>
+        <v>264.21530954</v>
       </c>
       <c r="Q83">
-        <v>654.03587201</v>
+        <v>641.31530954</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3091516794619937</v>
+        <v>0.3226806810489155</v>
       </c>
       <c r="T83">
-        <v>3.832087820434046</v>
+        <v>4.028951278110828</v>
       </c>
       <c r="U83">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V83">
         <v>0.3</v>
       </c>
       <c r="W83">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y83">
-        <v>2.275472581392496</v>
+        <v>2.149538451426536</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09487592258880476</v>
+        <v>0.09466832607983074</v>
       </c>
       <c r="C84">
-        <v>2965.921877498161</v>
+        <v>2936.754757590807</v>
       </c>
       <c r="D84">
-        <v>7839.279877498161</v>
+        <v>7872.581757590808</v>
       </c>
       <c r="E84">
-        <v>4101.958000000001</v>
+        <v>4164.427000000001</v>
       </c>
       <c r="F84">
-        <v>5122.458000000001</v>
+        <v>5184.927000000001</v>
       </c>
       <c r="G84">
         <v>249.1</v>
@@ -8181,28 +8181,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M84">
-        <v>328.3495578000001</v>
+        <v>332.3538207000001</v>
       </c>
       <c r="N84">
-        <v>377.4504422</v>
+        <v>373.4461793</v>
       </c>
       <c r="O84">
-        <v>113.23513266</v>
+        <v>112.03385379</v>
       </c>
       <c r="P84">
-        <v>264.21530954</v>
+        <v>261.41232551</v>
       </c>
       <c r="Q84">
-        <v>641.31530954</v>
+        <v>638.51232551</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3226806810489155</v>
+        <v>0.3378013298813574</v>
       </c>
       <c r="T84">
-        <v>4.028951278110828</v>
+        <v>4.248975142573114</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.149538451426536</v>
+        <v>2.123640397794891</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09466832607983074</v>
+        <v>0.09446072957085672</v>
       </c>
       <c r="C85">
-        <v>2936.754757590807</v>
+        <v>2907.871782788162</v>
       </c>
       <c r="D85">
-        <v>7872.581757590808</v>
+        <v>7906.167782788162</v>
       </c>
       <c r="E85">
-        <v>4164.427000000001</v>
+        <v>4226.896000000001</v>
       </c>
       <c r="F85">
-        <v>5184.927000000001</v>
+        <v>5247.396000000001</v>
       </c>
       <c r="G85">
         <v>249.1</v>
@@ -8263,28 +8263,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M85">
-        <v>332.3538207000001</v>
+        <v>336.3580836</v>
       </c>
       <c r="N85">
-        <v>373.4461793</v>
+        <v>369.4419164</v>
       </c>
       <c r="O85">
-        <v>112.03385379</v>
+        <v>110.83257492</v>
       </c>
       <c r="P85">
-        <v>261.41232551</v>
+        <v>258.60934148</v>
       </c>
       <c r="Q85">
-        <v>638.51232551</v>
+        <v>635.70934148</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3378013298813574</v>
+        <v>0.3548120598178547</v>
       </c>
       <c r="T85">
-        <v>4.248975142573114</v>
+        <v>4.496501990093186</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.123640397794891</v>
+        <v>2.098358964487809</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09446072957085672</v>
+        <v>0.09425313306188271</v>
       </c>
       <c r="C86">
-        <v>2907.871782788163</v>
+        <v>2879.276605332792</v>
       </c>
       <c r="D86">
-        <v>7906.167782788162</v>
+        <v>7940.041605332792</v>
       </c>
       <c r="E86">
-        <v>4226.896</v>
+        <v>4289.365</v>
       </c>
       <c r="F86">
-        <v>5247.396</v>
+        <v>5309.865</v>
       </c>
       <c r="G86">
         <v>249.1</v>
@@ -8345,28 +8345,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M86">
-        <v>336.3580836</v>
+        <v>340.3623465</v>
       </c>
       <c r="N86">
-        <v>369.4419164000001</v>
+        <v>365.4376535000001</v>
       </c>
       <c r="O86">
-        <v>110.83257492</v>
+        <v>109.63129605</v>
       </c>
       <c r="P86">
-        <v>258.6093414800001</v>
+        <v>255.8063574500001</v>
       </c>
       <c r="Q86">
-        <v>635.7093414800001</v>
+        <v>632.9063574500001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3548120598178544</v>
+        <v>0.3740908870792179</v>
       </c>
       <c r="T86">
-        <v>4.496501990093183</v>
+        <v>4.777032417282598</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.09835896448781</v>
+        <v>2.073672388435011</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09425313306188271</v>
+        <v>0.09404553655290866</v>
       </c>
       <c r="C87">
-        <v>2879.276605332792</v>
+        <v>2850.972940328457</v>
       </c>
       <c r="D87">
-        <v>7940.041605332792</v>
+        <v>7974.206940328458</v>
       </c>
       <c r="E87">
-        <v>4289.365</v>
+        <v>4351.834</v>
       </c>
       <c r="F87">
-        <v>5309.865</v>
+        <v>5372.334</v>
       </c>
       <c r="G87">
         <v>249.1</v>
@@ -8427,28 +8427,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M87">
-        <v>340.3623465</v>
+        <v>344.3666094</v>
       </c>
       <c r="N87">
-        <v>365.4376535000001</v>
+        <v>361.4333906000001</v>
       </c>
       <c r="O87">
-        <v>109.63129605</v>
+        <v>108.43001718</v>
       </c>
       <c r="P87">
-        <v>255.8063574500001</v>
+        <v>253.0033734200001</v>
       </c>
       <c r="Q87">
-        <v>632.9063574500001</v>
+        <v>630.10337342</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3740908870792179</v>
+        <v>0.3961238325207762</v>
       </c>
       <c r="T87">
-        <v>4.777032417282598</v>
+        <v>5.097638619784785</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.073672388435011</v>
+        <v>2.049559918802046</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09404553655290866</v>
+        <v>0.09383794004393464</v>
       </c>
       <c r="C88">
-        <v>2850.972940328457</v>
+        <v>2822.964567098354</v>
       </c>
       <c r="D88">
-        <v>7974.206940328458</v>
+        <v>8008.667567098353</v>
       </c>
       <c r="E88">
-        <v>4351.834</v>
+        <v>4414.303</v>
       </c>
       <c r="F88">
-        <v>5372.334</v>
+        <v>5434.803</v>
       </c>
       <c r="G88">
         <v>249.1</v>
@@ -8509,28 +8509,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M88">
-        <v>344.3666094</v>
+        <v>348.3708723</v>
       </c>
       <c r="N88">
-        <v>361.4333906000001</v>
+        <v>357.4291277</v>
       </c>
       <c r="O88">
-        <v>108.43001718</v>
+        <v>107.22873831</v>
       </c>
       <c r="P88">
-        <v>253.0033734200001</v>
+        <v>250.20038939</v>
       </c>
       <c r="Q88">
-        <v>630.10337342</v>
+        <v>627.3003893900001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3961238325207762</v>
+        <v>0.4215464618764203</v>
       </c>
       <c r="T88">
-        <v>5.097638619784785</v>
+        <v>5.467568853441156</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.049559918802046</v>
+        <v>2.026001758815816</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09383794004393464</v>
+        <v>0.09363034353496064</v>
       </c>
       <c r="C89">
-        <v>2822.964567098354</v>
+        <v>2795.255330578783</v>
       </c>
       <c r="D89">
-        <v>8008.667567098353</v>
+        <v>8043.427330578783</v>
       </c>
       <c r="E89">
-        <v>4414.303</v>
+        <v>4476.772</v>
       </c>
       <c r="F89">
-        <v>5434.803</v>
+        <v>5497.272</v>
       </c>
       <c r="G89">
         <v>249.1</v>
@@ -8591,28 +8591,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M89">
-        <v>348.3708723</v>
+        <v>352.3751352</v>
       </c>
       <c r="N89">
-        <v>357.4291277</v>
+        <v>353.4248648</v>
       </c>
       <c r="O89">
-        <v>107.22873831</v>
+        <v>106.02745944</v>
       </c>
       <c r="P89">
-        <v>250.20038939</v>
+        <v>247.39740536</v>
       </c>
       <c r="Q89">
-        <v>627.3003893900001</v>
+        <v>624.49740536</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4215464618764203</v>
+        <v>0.4512061961246719</v>
       </c>
       <c r="T89">
-        <v>5.467568853441156</v>
+        <v>5.899154126040256</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.026001758815816</v>
+        <v>2.002979011556545</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09363034353496064</v>
+        <v>0.09828214702598659</v>
       </c>
       <c r="C90">
-        <v>2795.255330578783</v>
+        <v>2019.84973296449</v>
       </c>
       <c r="D90">
-        <v>8043.427330578783</v>
+        <v>7330.490732964489</v>
       </c>
       <c r="E90">
-        <v>4476.772</v>
+        <v>4539.241</v>
       </c>
       <c r="F90">
-        <v>5497.272</v>
+        <v>5559.741</v>
       </c>
       <c r="G90">
         <v>249.1</v>
@@ -8673,45 +8673,45 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M90">
-        <v>352.3751352</v>
+        <v>399.7453779000001</v>
       </c>
       <c r="N90">
-        <v>353.4248648</v>
+        <v>306.0546221</v>
       </c>
       <c r="O90">
-        <v>106.02745944</v>
+        <v>91.81638663</v>
       </c>
       <c r="P90">
-        <v>247.39740536</v>
+        <v>214.23823547</v>
       </c>
       <c r="Q90">
-        <v>624.49740536</v>
+        <v>591.33823547</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4512061961246719</v>
+        <v>0.4862586093271509</v>
       </c>
       <c r="T90">
-        <v>5.899154126040256</v>
+        <v>6.409209448202827</v>
       </c>
       <c r="U90">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V90">
         <v>0.3</v>
       </c>
       <c r="W90">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y90">
-        <v>2.002979011556545</v>
+        <v>1.765623917174003</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09828214702598659</v>
+        <v>0.1005861505170126</v>
       </c>
       <c r="C91">
-        <v>2019.84973296449</v>
+        <v>1649.100700870628</v>
       </c>
       <c r="D91">
-        <v>7330.490732964489</v>
+        <v>7022.210700870628</v>
       </c>
       <c r="E91">
-        <v>4539.241</v>
+        <v>4601.71</v>
       </c>
       <c r="F91">
-        <v>5559.741</v>
+        <v>5622.21</v>
       </c>
       <c r="G91">
         <v>249.1</v>
@@ -8755,45 +8755,45 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M91">
-        <v>399.7453779000001</v>
+        <v>426.163518</v>
       </c>
       <c r="N91">
-        <v>306.0546221</v>
+        <v>279.6364820000001</v>
       </c>
       <c r="O91">
-        <v>91.81638663</v>
+        <v>83.89094460000001</v>
       </c>
       <c r="P91">
-        <v>214.23823547</v>
+        <v>195.7455374</v>
       </c>
       <c r="Q91">
-        <v>591.33823547</v>
+        <v>572.8455374</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4862586093271509</v>
+        <v>0.5283215051701258</v>
       </c>
       <c r="T91">
-        <v>6.409209448202827</v>
+        <v>7.021275834797914</v>
       </c>
       <c r="U91">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V91">
         <v>0.3</v>
       </c>
       <c r="W91">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y91">
-        <v>1.765623917174003</v>
+        <v>1.656171798356517</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1005861505170126</v>
+        <v>0.1004604540080385</v>
       </c>
       <c r="C92">
-        <v>1649.100700870628</v>
+        <v>1602.779890387123</v>
       </c>
       <c r="D92">
-        <v>7022.210700870628</v>
+        <v>7038.358890387123</v>
       </c>
       <c r="E92">
-        <v>4601.71</v>
+        <v>4664.179</v>
       </c>
       <c r="F92">
-        <v>5622.21</v>
+        <v>5684.679</v>
       </c>
       <c r="G92">
         <v>249.1</v>
@@ -8837,28 +8837,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M92">
-        <v>426.163518</v>
+        <v>430.8986682</v>
       </c>
       <c r="N92">
-        <v>279.6364820000001</v>
+        <v>274.9013318</v>
       </c>
       <c r="O92">
-        <v>83.89094460000001</v>
+        <v>82.47039954</v>
       </c>
       <c r="P92">
-        <v>195.7455374</v>
+        <v>192.43093226</v>
       </c>
       <c r="Q92">
-        <v>572.8455374</v>
+        <v>569.5309322600001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5283215051701258</v>
+        <v>0.5797317112004284</v>
       </c>
       <c r="T92">
-        <v>7.021275834797914</v>
+        <v>7.769356973969686</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.656171798356517</v>
+        <v>1.637972108264687</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1004604540080385</v>
+        <v>0.1003347574990645</v>
       </c>
       <c r="C93">
-        <v>1602.779890387123</v>
+        <v>1556.533519440588</v>
       </c>
       <c r="D93">
-        <v>7038.358890387123</v>
+        <v>7054.581519440588</v>
       </c>
       <c r="E93">
-        <v>4664.179</v>
+        <v>4726.648</v>
       </c>
       <c r="F93">
-        <v>5684.679</v>
+        <v>5747.148</v>
       </c>
       <c r="G93">
         <v>249.1</v>
@@ -8919,28 +8919,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M93">
-        <v>430.8986682</v>
+        <v>435.6338184000001</v>
       </c>
       <c r="N93">
-        <v>274.9013318</v>
+        <v>270.1661816</v>
       </c>
       <c r="O93">
-        <v>82.47039954</v>
+        <v>81.04985448000001</v>
       </c>
       <c r="P93">
-        <v>192.43093226</v>
+        <v>189.11632712</v>
       </c>
       <c r="Q93">
-        <v>569.5309322600001</v>
+        <v>566.21632712</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5797317112004284</v>
+        <v>0.6439944687383068</v>
       </c>
       <c r="T93">
-        <v>7.769356973969686</v>
+        <v>8.704458397934403</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.637972108264687</v>
+        <v>1.620168063609636</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1003347574990645</v>
+        <v>0.1002090609900905</v>
       </c>
       <c r="C94">
-        <v>1556.533519440588</v>
+        <v>1510.362103944533</v>
       </c>
       <c r="D94">
-        <v>7054.581519440588</v>
+        <v>7070.879103944533</v>
       </c>
       <c r="E94">
-        <v>4726.648</v>
+        <v>4789.117</v>
       </c>
       <c r="F94">
-        <v>5747.148</v>
+        <v>5809.617</v>
       </c>
       <c r="G94">
         <v>249.1</v>
@@ -9001,28 +9001,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M94">
-        <v>435.6338184000001</v>
+        <v>440.3689686000001</v>
       </c>
       <c r="N94">
-        <v>270.1661816</v>
+        <v>265.4310314</v>
       </c>
       <c r="O94">
-        <v>81.04985448000001</v>
+        <v>79.62930942</v>
       </c>
       <c r="P94">
-        <v>189.11632712</v>
+        <v>185.80172198</v>
       </c>
       <c r="Q94">
-        <v>566.21632712</v>
+        <v>562.90172198</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6439944687383068</v>
+        <v>0.7266180141441504</v>
       </c>
       <c r="T94">
-        <v>8.704458397934403</v>
+        <v>9.906731657317609</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.620168063609636</v>
+        <v>1.602746901635339</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1002090609900905</v>
+        <v>0.1000833644811165</v>
       </c>
       <c r="C95">
-        <v>1510.362103944533</v>
+        <v>1464.266164590991</v>
       </c>
       <c r="D95">
-        <v>7070.879103944533</v>
+        <v>7087.252164590991</v>
       </c>
       <c r="E95">
-        <v>4789.117</v>
+        <v>4851.586</v>
       </c>
       <c r="F95">
-        <v>5809.617</v>
+        <v>5872.086</v>
       </c>
       <c r="G95">
         <v>249.1</v>
@@ -9083,28 +9083,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M95">
-        <v>440.3689686000001</v>
+        <v>445.1041188</v>
       </c>
       <c r="N95">
-        <v>265.4310314</v>
+        <v>260.6958812</v>
       </c>
       <c r="O95">
-        <v>79.62930942</v>
+        <v>78.20876436</v>
       </c>
       <c r="P95">
-        <v>185.80172198</v>
+        <v>182.48711684</v>
       </c>
       <c r="Q95">
-        <v>562.90172198</v>
+        <v>559.58711684</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7266180141441504</v>
+        <v>0.836782741351942</v>
       </c>
       <c r="T95">
-        <v>9.906731657317609</v>
+        <v>11.50976266982855</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.602746901635339</v>
+        <v>1.585696402681772</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1000833644811165</v>
+        <v>0.09995766797214245</v>
       </c>
       <c r="C96">
-        <v>1464.266164590991</v>
+        <v>1418.246226905972</v>
       </c>
       <c r="D96">
-        <v>7087.252164590991</v>
+        <v>7103.701226905971</v>
       </c>
       <c r="E96">
-        <v>4851.586</v>
+        <v>4914.055</v>
       </c>
       <c r="F96">
-        <v>5872.086</v>
+        <v>5934.555</v>
       </c>
       <c r="G96">
         <v>249.1</v>
@@ -9165,28 +9165,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M96">
-        <v>445.1041188</v>
+        <v>449.8392690000001</v>
       </c>
       <c r="N96">
-        <v>260.6958812</v>
+        <v>255.960731</v>
       </c>
       <c r="O96">
-        <v>78.20876436</v>
+        <v>76.78821929999999</v>
       </c>
       <c r="P96">
-        <v>182.48711684</v>
+        <v>179.1725117</v>
       </c>
       <c r="Q96">
-        <v>559.58711684</v>
+        <v>556.2725117</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.836782741351942</v>
+        <v>0.9910133594428502</v>
       </c>
       <c r="T96">
-        <v>11.50976266982855</v>
+        <v>13.75400608734387</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.585696402681772</v>
+        <v>1.569004861600911</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09995766797214245</v>
+        <v>0.09983197146316843</v>
       </c>
       <c r="C97">
-        <v>1418.246226905972</v>
+        <v>1372.302821305673</v>
       </c>
       <c r="D97">
-        <v>7103.701226905971</v>
+        <v>7120.226821305673</v>
       </c>
       <c r="E97">
-        <v>4914.055</v>
+        <v>4976.524</v>
       </c>
       <c r="F97">
-        <v>5934.555</v>
+        <v>5997.024</v>
       </c>
       <c r="G97">
         <v>249.1</v>
@@ -9247,28 +9247,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M97">
-        <v>449.8392690000001</v>
+        <v>454.5744192000001</v>
       </c>
       <c r="N97">
-        <v>255.960731</v>
+        <v>251.2255808</v>
       </c>
       <c r="O97">
-        <v>76.78821929999999</v>
+        <v>75.36767424</v>
       </c>
       <c r="P97">
-        <v>179.1725117</v>
+        <v>175.85790656</v>
       </c>
       <c r="Q97">
-        <v>556.2725117</v>
+        <v>552.9579065600001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9910133594428502</v>
+        <v>1.222359286579213</v>
       </c>
       <c r="T97">
-        <v>13.75400608734387</v>
+        <v>17.12037121361686</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.569004861600911</v>
+        <v>1.552661060959235</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09983197146316844</v>
+        <v>0.0997062749541944</v>
       </c>
       <c r="C98">
-        <v>1372.302821305673</v>
+        <v>1326.436483153517</v>
       </c>
       <c r="D98">
-        <v>7120.226821305672</v>
+        <v>7136.829483153516</v>
       </c>
       <c r="E98">
-        <v>4976.523999999999</v>
+        <v>5038.992999999999</v>
       </c>
       <c r="F98">
-        <v>5997.023999999999</v>
+        <v>6059.492999999999</v>
       </c>
       <c r="G98">
         <v>249.1</v>
@@ -9329,28 +9329,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M98">
-        <v>454.5744192</v>
+        <v>459.3095694</v>
       </c>
       <c r="N98">
-        <v>251.2255808</v>
+        <v>246.4904306000001</v>
       </c>
       <c r="O98">
-        <v>75.36767424000001</v>
+        <v>73.94712918000002</v>
       </c>
       <c r="P98">
-        <v>175.85790656</v>
+        <v>172.5433014200001</v>
       </c>
       <c r="Q98">
-        <v>552.9579065600001</v>
+        <v>549.6433014200001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.22235928657921</v>
+        <v>1.607935831806479</v>
       </c>
       <c r="T98">
-        <v>17.12037121361681</v>
+        <v>22.7309797574051</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.552661060959235</v>
+        <v>1.5366542458978</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.0997062749541944</v>
+        <v>0.09958057844522039</v>
       </c>
       <c r="C99">
-        <v>1326.436483153517</v>
+        <v>1280.647752817945</v>
       </c>
       <c r="D99">
-        <v>7136.829483153516</v>
+        <v>7153.509752817944</v>
       </c>
       <c r="E99">
-        <v>5038.992999999999</v>
+        <v>5101.462</v>
       </c>
       <c r="F99">
-        <v>6059.492999999999</v>
+        <v>6121.962</v>
       </c>
       <c r="G99">
         <v>249.1</v>
@@ -9411,28 +9411,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M99">
-        <v>459.3095694</v>
+        <v>464.0447196</v>
       </c>
       <c r="N99">
-        <v>246.4904306000001</v>
+        <v>241.7552804000001</v>
       </c>
       <c r="O99">
-        <v>73.94712918000002</v>
+        <v>72.52658412000001</v>
       </c>
       <c r="P99">
-        <v>172.5433014200001</v>
+        <v>169.2286962800001</v>
       </c>
       <c r="Q99">
-        <v>549.6433014200001</v>
+        <v>546.32869628</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.607935831806479</v>
+        <v>2.379088922261017</v>
       </c>
       <c r="T99">
-        <v>22.7309797574051</v>
+        <v>33.95219684498166</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.5366542458978</v>
+        <v>1.520974100531495</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09958057844522039</v>
+        <v>0.09945488193624635</v>
       </c>
       <c r="C100">
-        <v>1280.647752817945</v>
+        <v>1234.937175731061</v>
       </c>
       <c r="D100">
-        <v>7153.509752817944</v>
+        <v>7170.26817573106</v>
       </c>
       <c r="E100">
-        <v>5101.462</v>
+        <v>5163.931</v>
       </c>
       <c r="F100">
-        <v>6121.962</v>
+        <v>6184.431</v>
       </c>
       <c r="G100">
         <v>249.1</v>
@@ -9493,28 +9493,28 @@
         <v>705.8000000000001</v>
       </c>
       <c r="M100">
-        <v>464.0447196</v>
+        <v>468.7798698</v>
       </c>
       <c r="N100">
-        <v>241.7552804000001</v>
+        <v>237.0201302</v>
       </c>
       <c r="O100">
-        <v>72.52658412000001</v>
+        <v>71.10603906000001</v>
       </c>
       <c r="P100">
-        <v>169.2286962800001</v>
+        <v>165.91409114</v>
       </c>
       <c r="Q100">
-        <v>546.32869628</v>
+        <v>543.0140911400001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.379088922261017</v>
+        <v>4.692548193624631</v>
       </c>
       <c r="T100">
-        <v>33.95219684498166</v>
+        <v>67.61584810771136</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.520974100531495</v>
+        <v>1.505610725778652</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09945488193624635</v>
-      </c>
-      <c r="C101">
-        <v>1234.937175731061</v>
-      </c>
-      <c r="D101">
-        <v>7170.26817573106</v>
-      </c>
-      <c r="E101">
-        <v>5163.931</v>
-      </c>
-      <c r="F101">
-        <v>6184.431</v>
-      </c>
-      <c r="G101">
-        <v>249.1</v>
-      </c>
-      <c r="H101">
-        <v>5226.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1082.9</v>
-      </c>
-      <c r="K101">
-        <v>377.1</v>
-      </c>
-      <c r="L101">
-        <v>705.8000000000001</v>
-      </c>
-      <c r="M101">
-        <v>468.7798698</v>
-      </c>
-      <c r="N101">
-        <v>237.0201302</v>
-      </c>
-      <c r="O101">
-        <v>71.10603906000001</v>
-      </c>
-      <c r="P101">
-        <v>165.91409114</v>
-      </c>
-      <c r="Q101">
-        <v>543.0140911400001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.692548193624631</v>
-      </c>
-      <c r="T101">
-        <v>67.61584810771136</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.05306</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.505610725778652</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
